--- a/MomijiStore_OS/02_Analytics/SourceData/楽天RPP広告分析.xlsx
+++ b/MomijiStore_OS/02_Analytics/SourceData/楽天RPP広告分析.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hide0726/Desktop/Claude Code/MomijiStore_OS/02_Analytics/SourceData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_DABE5FBE975A7AEE626CD4B45B5DCE3AF7474A63" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_58D36C9A21FF80DE14D087B7E72D097BD8FCD642" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7月" sheetId="1" r:id="rId1"/>
+    <sheet name="8月" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="339">
   <si>
     <t>RPP広告分析</t>
   </si>
@@ -924,6 +925,132 @@
   </si>
   <si>
     <t>合計</t>
+  </si>
+  <si>
+    <t>2026年08月</t>
+  </si>
+  <si>
+    <t>【3本セット】アース製薬 らくハピ お部屋の防カビ剤 カチッとおすだけ 無香料 60mL 約2カ月持続 防カビ カビ予防</t>
+  </si>
+  <si>
+    <t>b0hc1kzx44</t>
+  </si>
+  <si>
+    <t>【6種セット】クーリア クリアジェムステッカー エンジェル ストロベリー レモン グレープ ソーダ プラネット デコレー</t>
+  </si>
+  <si>
+    <t>【2個セット】ファブリーズ W除菌+消臭スプレー 衣類・布製品用 無香料 アルコール成分配合 本体 370mL×2個セッ</t>
+  </si>
+  <si>
+    <t>b0f9dzl2mg</t>
+  </si>
+  <si>
+    <t>【2個セット】DERMASHARE ダーマシェア バクチオール マルチバーム 13g 美容液スティック スティックバーム</t>
+  </si>
+  <si>
+    <t>b0hg1f5b7t</t>
+  </si>
+  <si>
+    <t>b09l7qd1hp</t>
+  </si>
+  <si>
+    <t>b07bgstt34</t>
+  </si>
+  <si>
+    <t>【2個セット】グレイシアハイジーン ニトリルグローブ XS GH-01 125枚入×2個セット ニトリル手袋 パウダーフ</t>
+  </si>
+  <si>
+    <t>【6種セット】クーリア ウォーターシール スイートマジカル はむはむハムちゃん チャーミングルーム きらりんエナガマーチ</t>
+  </si>
+  <si>
+    <t>b01g81swcm</t>
+  </si>
+  <si>
+    <t>b0ctt9m27s</t>
+  </si>
+  <si>
+    <t>b0hg6v7qy1</t>
+  </si>
+  <si>
+    <t>b0hg1t7vg8</t>
+  </si>
+  <si>
+    <t>4580313723736</t>
+  </si>
+  <si>
+    <t>b0gvxq7xpv</t>
+  </si>
+  <si>
+    <t>【2026年限定】ランドリン 柔軟剤 フレッシュモヒート 600mL 本体 液体 柔軟仕上げ剤 夏季限定 サマー 清涼感</t>
+  </si>
+  <si>
+    <t>b0hg1dql38</t>
+  </si>
+  <si>
+    <t>【2個セット】アリエール ジェルボール4D 微香 詰め替え メガジャンボ 83個×2個セット P&amp;G 洗濯洗剤 ジェルボ</t>
+  </si>
+  <si>
+    <t>b002wgto52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【6個セット】IROKA イロカ フレアフレグランス ネイキッドリリーの香り 詰め替え 1200mL×6個セット 花王 </t>
+  </si>
+  <si>
+    <t>b0dmp16lqs</t>
+  </si>
+  <si>
+    <t>b09xxsmk31</t>
+  </si>
+  <si>
+    <t>b0867jpktd</t>
+  </si>
+  <si>
+    <t>b0f74cphd1</t>
+  </si>
+  <si>
+    <t>b0hd77wvwr</t>
+  </si>
+  <si>
+    <t>【セット品】レノア アロマジュエル Perfume N°7 ジャスミンローズの香り 本体420mL 詰め替え1410mL</t>
+  </si>
+  <si>
+    <t>b01dn6zigi</t>
+  </si>
+  <si>
+    <t>【2個セット】プライバシー UVパウダー SPF50+ PA++++ メイクの上から使える UVカット フェイスパウダー</t>
+  </si>
+  <si>
+    <t>【3本セット】NEWクレラップ お徳用 22cm×50m 日本製 キッチンラップ 電子レンジ対応 食品保存 冷蔵保存 冷</t>
+  </si>
+  <si>
+    <t>レノア 超消臭 煮沸レベル 抗菌ビーズ スポーツ クールリフレッシュ＆シトラス 詰め替え 超特大 1410mL×2個セッ</t>
+  </si>
+  <si>
+    <t>Nuxe(ニュクス) プロディジューオイル 50mL ヘアオイル ボディオイル フェイスオイル 全身用 マルチ美容オイル</t>
+  </si>
+  <si>
+    <t>【セット品】ファブリーズ W除菌+消臭スプレー 衣類・布製品用 香りが残らない 本体370mL＋つめかえ4回分1280m</t>
+  </si>
+  <si>
+    <t>デビフ おすわりくん 超小粒 ササミ ７５ｇ ×４袋セット 犬用 おやつ</t>
+  </si>
+  <si>
+    <t>【4個セット】日本カルシウム工業 ヘルシーウォーターEX 38g×4個セット ペットボトル用 浄水パック 携帯浄水器 カ</t>
+  </si>
+  <si>
+    <t>Anker Eufy ユーフィ SmartTrack Card E30×2個セット 充電式紛失防止トラッカー スマートタ</t>
+  </si>
+  <si>
+    <t>【セット品】いなば チャオ 焼かつおディナー 高齢猫用 2種アソートセット 50g×16袋 国産 猫 猫用 キャットフー</t>
+  </si>
+  <si>
+    <t>【2個セット】柑橘王子 メラノサーチ VitaC洗顔 120g×2本 洗顔フォーム メンズ ビタミンC誘導体 毛穴 ケア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【2個セット】レノア アロマジュエル Perfume ブルーミングブロッサムの香り 詰め替え 1410mL×2個セット </t>
+  </si>
+  <si>
+    <t>【2本セット】ムシクリン カメムシ用ジャンボエアゾール 550ml アース製薬 カメムシ対策 侵入防止 スプレー 屋外用</t>
   </si>
 </sst>
 </file>
@@ -933,7 +1060,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -959,6 +1086,17 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -980,7 +1118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -989,6 +1127,13 @@
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -10937,4 +11082,6267 @@
   <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:P135"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="12" max="13" width="13" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="10">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="11">
+        <v>0.88489999999999991</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="10">
+        <v>53095</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="10">
+        <v>3781</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="10">
+        <v>218218</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="11">
+        <v>4.1098999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="11">
+        <v>1.6899999999999998E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="C13" s="9">
+        <v>22</v>
+      </c>
+      <c r="D13" s="9">
+        <v>308</v>
+      </c>
+      <c r="E13" s="12">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="F13" s="9">
+        <v>4426</v>
+      </c>
+      <c r="G13" s="9">
+        <v>15</v>
+      </c>
+      <c r="H13" s="9">
+        <v>41720</v>
+      </c>
+      <c r="I13" s="9">
+        <v>8</v>
+      </c>
+      <c r="J13" s="12">
+        <v>2.5899999999999999E-2</v>
+      </c>
+      <c r="K13" s="13">
+        <f t="shared" ref="K13:K44" si="0">IF(F13=0,"",H13/F13)</f>
+        <v>9.4261183913239943</v>
+      </c>
+      <c r="L13" s="9">
+        <v>38740</v>
+      </c>
+      <c r="M13" s="10">
+        <v>53640</v>
+      </c>
+      <c r="N13" s="11">
+        <f t="shared" ref="N13:N44" si="1">IF(OR(M13="",M13=0),"",H13/M13)</f>
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="O13" s="10">
+        <v>15732</v>
+      </c>
+      <c r="P13" s="11">
+        <f t="shared" ref="P13:P44" si="2">IF(OR(O13="",O13=0),"",F13/O13)</f>
+        <v>0.28133740147470127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="C14" s="9">
+        <v>20</v>
+      </c>
+      <c r="D14" s="9">
+        <v>192</v>
+      </c>
+      <c r="E14" s="12">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="F14" s="9">
+        <v>3495</v>
+      </c>
+      <c r="G14" s="9">
+        <v>19</v>
+      </c>
+      <c r="H14" s="9">
+        <v>2980</v>
+      </c>
+      <c r="I14" s="9">
+        <v>1</v>
+      </c>
+      <c r="J14" s="12">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="K14" s="13">
+        <f t="shared" si="0"/>
+        <v>0.85264663805436336</v>
+      </c>
+      <c r="L14" s="9">
+        <v>2980</v>
+      </c>
+      <c r="M14" s="10">
+        <v>33740</v>
+      </c>
+      <c r="N14" s="11">
+        <f t="shared" si="1"/>
+        <v>8.8322465915826917E-2</v>
+      </c>
+      <c r="O14" s="10">
+        <v>28679</v>
+      </c>
+      <c r="P14" s="11">
+        <f t="shared" si="2"/>
+        <v>0.12186617385543429</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="9">
+        <v>22</v>
+      </c>
+      <c r="D15" s="9">
+        <v>190</v>
+      </c>
+      <c r="E15" s="12">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="F15" s="9">
+        <v>3461</v>
+      </c>
+      <c r="G15" s="9">
+        <v>19</v>
+      </c>
+      <c r="H15" s="9">
+        <v>22660</v>
+      </c>
+      <c r="I15" s="9">
+        <v>6</v>
+      </c>
+      <c r="J15" s="12">
+        <v>3.15E-2</v>
+      </c>
+      <c r="K15" s="13">
+        <f t="shared" si="0"/>
+        <v>6.5472406818838484</v>
+      </c>
+      <c r="L15" s="9">
+        <v>22660</v>
+      </c>
+      <c r="M15" s="10">
+        <v>89440</v>
+      </c>
+      <c r="N15" s="11">
+        <f t="shared" si="1"/>
+        <v>0.25335420393559926</v>
+      </c>
+      <c r="O15" s="10">
+        <v>39624</v>
+      </c>
+      <c r="P15" s="11">
+        <f t="shared" si="2"/>
+        <v>8.7346052897234003E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="9">
+        <v>20</v>
+      </c>
+      <c r="D16" s="9">
+        <v>275</v>
+      </c>
+      <c r="E16" s="12">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="F16" s="9">
+        <v>3355</v>
+      </c>
+      <c r="G16" s="9">
+        <v>13</v>
+      </c>
+      <c r="H16" s="9">
+        <v>21120</v>
+      </c>
+      <c r="I16" s="9">
+        <v>8</v>
+      </c>
+      <c r="J16" s="12">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="K16" s="13">
+        <f t="shared" si="0"/>
+        <v>6.2950819672131146</v>
+      </c>
+      <c r="L16" s="9">
+        <v>21120</v>
+      </c>
+      <c r="M16" s="10">
+        <v>18480</v>
+      </c>
+      <c r="N16" s="11">
+        <f t="shared" si="1"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="O16" s="10">
+        <v>4676</v>
+      </c>
+      <c r="P16" s="11">
+        <f t="shared" si="2"/>
+        <v>0.71749358426005128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="9">
+        <v>24</v>
+      </c>
+      <c r="D17" s="9">
+        <v>116</v>
+      </c>
+      <c r="E17" s="12">
+        <v>1.11E-2</v>
+      </c>
+      <c r="F17" s="9">
+        <v>2758</v>
+      </c>
+      <c r="G17" s="9">
+        <v>24</v>
+      </c>
+      <c r="H17" s="9">
+        <v>21680</v>
+      </c>
+      <c r="I17" s="9">
+        <v>6</v>
+      </c>
+      <c r="J17" s="12">
+        <v>5.1700000000000003E-2</v>
+      </c>
+      <c r="K17" s="13">
+        <f t="shared" si="0"/>
+        <v>7.8607686729514139</v>
+      </c>
+      <c r="L17" s="9">
+        <v>18200</v>
+      </c>
+      <c r="M17" s="10">
+        <v>21880</v>
+      </c>
+      <c r="N17" s="11">
+        <f t="shared" si="1"/>
+        <v>0.99085923217550276</v>
+      </c>
+      <c r="O17" s="10">
+        <v>6718</v>
+      </c>
+      <c r="P17" s="11">
+        <f t="shared" si="2"/>
+        <v>0.41053885084846681</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="9">
+        <v>20</v>
+      </c>
+      <c r="D18" s="9">
+        <v>131</v>
+      </c>
+      <c r="E18" s="12">
+        <v>0.1145</v>
+      </c>
+      <c r="F18" s="9">
+        <v>1640</v>
+      </c>
+      <c r="G18" s="9">
+        <v>13</v>
+      </c>
+      <c r="H18" s="9">
+        <v>15840</v>
+      </c>
+      <c r="I18" s="9">
+        <v>7</v>
+      </c>
+      <c r="J18" s="12">
+        <v>5.3400000000000003E-2</v>
+      </c>
+      <c r="K18" s="13">
+        <f t="shared" si="0"/>
+        <v>9.6585365853658534</v>
+      </c>
+      <c r="L18" s="9">
+        <v>14060</v>
+      </c>
+      <c r="M18" s="10">
+        <v>14240</v>
+      </c>
+      <c r="N18" s="11">
+        <f t="shared" si="1"/>
+        <v>1.1123595505617978</v>
+      </c>
+      <c r="O18" s="10">
+        <v>5112</v>
+      </c>
+      <c r="P18" s="11">
+        <f t="shared" si="2"/>
+        <v>0.32081377151799689</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="9">
+        <v>24</v>
+      </c>
+      <c r="D19" s="9">
+        <v>88</v>
+      </c>
+      <c r="E19" s="12">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="F19" s="9">
+        <v>1292</v>
+      </c>
+      <c r="G19" s="9">
+        <v>15</v>
+      </c>
+      <c r="H19" s="9">
+        <v>2980</v>
+      </c>
+      <c r="I19" s="9">
+        <v>1</v>
+      </c>
+      <c r="J19" s="12">
+        <v>1.1299999999999999E-2</v>
+      </c>
+      <c r="K19" s="13">
+        <f t="shared" si="0"/>
+        <v>2.3065015479876161</v>
+      </c>
+      <c r="L19" s="9">
+        <v>0</v>
+      </c>
+      <c r="M19" s="10">
+        <v>5960</v>
+      </c>
+      <c r="N19" s="11">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="O19" s="10">
+        <v>932</v>
+      </c>
+      <c r="P19" s="11">
+        <f t="shared" si="2"/>
+        <v>1.3862660944206009</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="9">
+        <v>20</v>
+      </c>
+      <c r="D20" s="9">
+        <v>91</v>
+      </c>
+      <c r="E20" s="12">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="F20" s="9">
+        <v>1288</v>
+      </c>
+      <c r="G20" s="9">
+        <v>15</v>
+      </c>
+      <c r="H20" s="9">
+        <v>7120</v>
+      </c>
+      <c r="I20" s="9">
+        <v>2</v>
+      </c>
+      <c r="J20" s="12">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="K20" s="13">
+        <f t="shared" si="0"/>
+        <v>5.5279503105590067</v>
+      </c>
+      <c r="L20" s="9">
+        <v>0</v>
+      </c>
+      <c r="M20" s="10">
+        <v>7120</v>
+      </c>
+      <c r="N20" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O20" s="10">
+        <v>3640</v>
+      </c>
+      <c r="P20" s="11">
+        <f t="shared" si="2"/>
+        <v>0.35384615384615387</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="9">
+        <v>24</v>
+      </c>
+      <c r="D21" s="9">
+        <v>45</v>
+      </c>
+      <c r="E21" s="12">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="F21" s="9">
+        <v>1152</v>
+      </c>
+      <c r="G21" s="9">
+        <v>26</v>
+      </c>
+      <c r="H21" s="9">
+        <v>15840</v>
+      </c>
+      <c r="I21" s="9">
+        <v>3</v>
+      </c>
+      <c r="J21" s="12">
+        <v>6.6600000000000006E-2</v>
+      </c>
+      <c r="K21" s="13">
+        <f t="shared" si="0"/>
+        <v>13.75</v>
+      </c>
+      <c r="L21" s="9">
+        <v>15840</v>
+      </c>
+      <c r="M21" s="10">
+        <v>17820</v>
+      </c>
+      <c r="N21" s="11">
+        <f t="shared" si="1"/>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="O21" s="10">
+        <v>7479</v>
+      </c>
+      <c r="P21" s="11">
+        <f t="shared" si="2"/>
+        <v>0.15403128760529483</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" s="9">
+        <v>24</v>
+      </c>
+      <c r="D22" s="9">
+        <v>88</v>
+      </c>
+      <c r="E22" s="12">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="F22" s="9">
+        <v>1140</v>
+      </c>
+      <c r="G22" s="9">
+        <v>13</v>
+      </c>
+      <c r="H22" s="9">
+        <v>0</v>
+      </c>
+      <c r="I22" s="9">
+        <v>0</v>
+      </c>
+      <c r="J22" s="12">
+        <v>0</v>
+      </c>
+      <c r="K22" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="9">
+        <v>0</v>
+      </c>
+      <c r="M22" s="10">
+        <v>2198</v>
+      </c>
+      <c r="N22" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O22" s="10">
+        <v>590</v>
+      </c>
+      <c r="P22" s="11">
+        <f t="shared" si="2"/>
+        <v>1.9322033898305084</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="9">
+        <v>20</v>
+      </c>
+      <c r="D23" s="9">
+        <v>88</v>
+      </c>
+      <c r="E23" s="12">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="F23" s="9">
+        <v>1113</v>
+      </c>
+      <c r="G23" s="9">
+        <v>13</v>
+      </c>
+      <c r="H23" s="9">
+        <v>9160</v>
+      </c>
+      <c r="I23" s="9">
+        <v>2</v>
+      </c>
+      <c r="J23" s="12">
+        <v>2.2700000000000001E-2</v>
+      </c>
+      <c r="K23" s="13">
+        <f t="shared" si="0"/>
+        <v>8.2300089847259663</v>
+      </c>
+      <c r="L23" s="9">
+        <v>4580</v>
+      </c>
+      <c r="M23" s="10">
+        <v>36640</v>
+      </c>
+      <c r="N23" s="11">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="O23" s="10">
+        <v>4136</v>
+      </c>
+      <c r="P23" s="11">
+        <f t="shared" si="2"/>
+        <v>0.26910058027079303</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="9">
+        <v>24</v>
+      </c>
+      <c r="D24" s="9">
+        <v>64</v>
+      </c>
+      <c r="E24" s="12">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="F24" s="9">
+        <v>929</v>
+      </c>
+      <c r="G24" s="9">
+        <v>15</v>
+      </c>
+      <c r="H24" s="9">
+        <v>0</v>
+      </c>
+      <c r="I24" s="9">
+        <v>0</v>
+      </c>
+      <c r="J24" s="12">
+        <v>0</v>
+      </c>
+      <c r="K24" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="9">
+        <v>0</v>
+      </c>
+      <c r="M24" s="10">
+        <v>18440</v>
+      </c>
+      <c r="N24" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O24" s="10">
+        <v>7874</v>
+      </c>
+      <c r="P24" s="11">
+        <f t="shared" si="2"/>
+        <v>0.11798323596647194</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C25" s="9">
+        <v>20</v>
+      </c>
+      <c r="D25" s="9">
+        <v>81</v>
+      </c>
+      <c r="E25" s="12">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="F25" s="9">
+        <v>906</v>
+      </c>
+      <c r="G25" s="9">
+        <v>12</v>
+      </c>
+      <c r="H25" s="9">
+        <v>2520</v>
+      </c>
+      <c r="I25" s="9">
+        <v>1</v>
+      </c>
+      <c r="J25" s="12">
+        <v>1.23E-2</v>
+      </c>
+      <c r="K25" s="13">
+        <f t="shared" si="0"/>
+        <v>2.7814569536423841</v>
+      </c>
+      <c r="L25" s="9">
+        <v>2520</v>
+      </c>
+      <c r="M25" s="10">
+        <v>2520</v>
+      </c>
+      <c r="N25" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O25" s="10">
+        <v>1042</v>
+      </c>
+      <c r="P25" s="11">
+        <f t="shared" si="2"/>
+        <v>0.86948176583493286</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C26" s="9">
+        <v>20</v>
+      </c>
+      <c r="D26" s="9">
+        <v>78</v>
+      </c>
+      <c r="E26" s="12">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="F26" s="9">
+        <v>890</v>
+      </c>
+      <c r="G26" s="9">
+        <v>12</v>
+      </c>
+      <c r="H26" s="9">
+        <v>4960</v>
+      </c>
+      <c r="I26" s="9">
+        <v>1</v>
+      </c>
+      <c r="J26" s="12">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="K26" s="13">
+        <f t="shared" si="0"/>
+        <v>5.5730337078651688</v>
+      </c>
+      <c r="L26" s="9">
+        <v>4960</v>
+      </c>
+      <c r="M26" s="10">
+        <v>25320</v>
+      </c>
+      <c r="N26" s="11">
+        <f t="shared" si="1"/>
+        <v>0.19589257503949448</v>
+      </c>
+      <c r="O26" s="10">
+        <v>1822</v>
+      </c>
+      <c r="P26" s="11">
+        <f t="shared" si="2"/>
+        <v>0.48847420417124038</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9">
+        <v>24</v>
+      </c>
+      <c r="D27" s="9">
+        <v>64</v>
+      </c>
+      <c r="E27" s="12">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="F27" s="9">
+        <v>857</v>
+      </c>
+      <c r="G27" s="9">
+        <v>14</v>
+      </c>
+      <c r="H27" s="9">
+        <v>0</v>
+      </c>
+      <c r="I27" s="9">
+        <v>0</v>
+      </c>
+      <c r="J27" s="12">
+        <v>0</v>
+      </c>
+      <c r="K27" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="9">
+        <v>0</v>
+      </c>
+      <c r="M27" s="10"/>
+      <c r="N27" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O27" s="10"/>
+      <c r="P27" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="9">
+        <v>24</v>
+      </c>
+      <c r="D28" s="9">
+        <v>63</v>
+      </c>
+      <c r="E28" s="12">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="F28" s="9">
+        <v>822</v>
+      </c>
+      <c r="G28" s="9">
+        <v>14</v>
+      </c>
+      <c r="H28" s="9">
+        <v>3980</v>
+      </c>
+      <c r="I28" s="9">
+        <v>1</v>
+      </c>
+      <c r="J28" s="12">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="K28" s="13">
+        <f t="shared" si="0"/>
+        <v>4.8418491484184916</v>
+      </c>
+      <c r="L28" s="9">
+        <v>3980</v>
+      </c>
+      <c r="M28" s="10">
+        <v>3980</v>
+      </c>
+      <c r="N28" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O28" s="10">
+        <v>1223</v>
+      </c>
+      <c r="P28" s="11">
+        <f t="shared" si="2"/>
+        <v>0.67211774325429274</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C29" s="9">
+        <v>20</v>
+      </c>
+      <c r="D29" s="9">
+        <v>77</v>
+      </c>
+      <c r="E29" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F29" s="9">
+        <v>821</v>
+      </c>
+      <c r="G29" s="9">
+        <v>11</v>
+      </c>
+      <c r="H29" s="9">
+        <v>0</v>
+      </c>
+      <c r="I29" s="9">
+        <v>0</v>
+      </c>
+      <c r="J29" s="12">
+        <v>0</v>
+      </c>
+      <c r="K29" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="9">
+        <v>0</v>
+      </c>
+      <c r="M29" s="10">
+        <v>1980</v>
+      </c>
+      <c r="N29" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O29" s="10">
+        <v>523</v>
+      </c>
+      <c r="P29" s="11">
+        <f t="shared" si="2"/>
+        <v>1.5697896749521989</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C30" s="9">
+        <v>20</v>
+      </c>
+      <c r="D30" s="9">
+        <v>77</v>
+      </c>
+      <c r="E30" s="12">
+        <v>3.8E-3</v>
+      </c>
+      <c r="F30" s="9">
+        <v>810</v>
+      </c>
+      <c r="G30" s="9">
+        <v>11</v>
+      </c>
+      <c r="H30" s="9">
+        <v>0</v>
+      </c>
+      <c r="I30" s="9">
+        <v>0</v>
+      </c>
+      <c r="J30" s="12">
+        <v>0</v>
+      </c>
+      <c r="K30" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="9">
+        <v>0</v>
+      </c>
+      <c r="M30" s="10">
+        <v>1980</v>
+      </c>
+      <c r="N30" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O30" s="10">
+        <v>891</v>
+      </c>
+      <c r="P30" s="11">
+        <f t="shared" si="2"/>
+        <v>0.90909090909090906</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="9">
+        <v>22</v>
+      </c>
+      <c r="D31" s="9">
+        <v>37</v>
+      </c>
+      <c r="E31" s="12">
+        <v>5.5000000000000014E-3</v>
+      </c>
+      <c r="F31" s="9">
+        <v>806</v>
+      </c>
+      <c r="G31" s="9">
+        <v>22</v>
+      </c>
+      <c r="H31" s="9">
+        <v>10680</v>
+      </c>
+      <c r="I31" s="9">
+        <v>5</v>
+      </c>
+      <c r="J31" s="12">
+        <v>0.1351</v>
+      </c>
+      <c r="K31" s="13">
+        <f t="shared" si="0"/>
+        <v>13.250620347394541</v>
+      </c>
+      <c r="L31" s="9">
+        <v>10680</v>
+      </c>
+      <c r="M31" s="10">
+        <v>10680</v>
+      </c>
+      <c r="N31" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O31" s="10">
+        <v>6582</v>
+      </c>
+      <c r="P31" s="11">
+        <f t="shared" si="2"/>
+        <v>0.1224551807961106</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9">
+        <v>22</v>
+      </c>
+      <c r="D32" s="9">
+        <v>54</v>
+      </c>
+      <c r="E32" s="12">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="F32" s="9">
+        <v>793</v>
+      </c>
+      <c r="G32" s="9">
+        <v>15</v>
+      </c>
+      <c r="H32" s="9">
+        <v>0</v>
+      </c>
+      <c r="I32" s="9">
+        <v>0</v>
+      </c>
+      <c r="J32" s="12">
+        <v>0</v>
+      </c>
+      <c r="K32" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="9">
+        <v>0</v>
+      </c>
+      <c r="M32" s="10"/>
+      <c r="N32" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O32" s="10"/>
+      <c r="P32" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="9">
+        <v>20</v>
+      </c>
+      <c r="D33" s="9">
+        <v>68</v>
+      </c>
+      <c r="E33" s="12">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="F33" s="9">
+        <v>780</v>
+      </c>
+      <c r="G33" s="9">
+        <v>12</v>
+      </c>
+      <c r="H33" s="9">
+        <v>0</v>
+      </c>
+      <c r="I33" s="9">
+        <v>0</v>
+      </c>
+      <c r="J33" s="12">
+        <v>0</v>
+      </c>
+      <c r="K33" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="9">
+        <v>0</v>
+      </c>
+      <c r="M33" s="10">
+        <v>4280</v>
+      </c>
+      <c r="N33" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O33" s="10">
+        <v>1038</v>
+      </c>
+      <c r="P33" s="11">
+        <f t="shared" si="2"/>
+        <v>0.75144508670520227</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9">
+        <v>22</v>
+      </c>
+      <c r="D34" s="9">
+        <v>48</v>
+      </c>
+      <c r="E34" s="12">
+        <v>1.9E-3</v>
+      </c>
+      <c r="F34" s="9">
+        <v>697</v>
+      </c>
+      <c r="G34" s="9">
+        <v>15</v>
+      </c>
+      <c r="H34" s="9">
+        <v>0</v>
+      </c>
+      <c r="I34" s="9">
+        <v>0</v>
+      </c>
+      <c r="J34" s="12">
+        <v>0</v>
+      </c>
+      <c r="K34" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="9">
+        <v>0</v>
+      </c>
+      <c r="M34" s="10"/>
+      <c r="N34" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O34" s="10"/>
+      <c r="P34" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" s="9">
+        <v>22</v>
+      </c>
+      <c r="D35" s="9">
+        <v>57</v>
+      </c>
+      <c r="E35" s="12">
+        <v>5.5000000000000014E-3</v>
+      </c>
+      <c r="F35" s="9">
+        <v>688</v>
+      </c>
+      <c r="G35" s="9">
+        <v>13</v>
+      </c>
+      <c r="H35" s="9">
+        <v>2980</v>
+      </c>
+      <c r="I35" s="9">
+        <v>1</v>
+      </c>
+      <c r="J35" s="12">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="K35" s="13">
+        <f t="shared" si="0"/>
+        <v>4.3313953488372094</v>
+      </c>
+      <c r="L35" s="9">
+        <v>2980</v>
+      </c>
+      <c r="M35" s="10">
+        <v>2980</v>
+      </c>
+      <c r="N35" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O35" s="10">
+        <v>795</v>
+      </c>
+      <c r="P35" s="11">
+        <f t="shared" si="2"/>
+        <v>0.86540880503144657</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="C36" s="9">
+        <v>20</v>
+      </c>
+      <c r="D36" s="9">
+        <v>52</v>
+      </c>
+      <c r="E36" s="12">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="F36" s="9">
+        <v>680</v>
+      </c>
+      <c r="G36" s="9">
+        <v>14</v>
+      </c>
+      <c r="H36" s="9">
+        <v>1980</v>
+      </c>
+      <c r="I36" s="9">
+        <v>1</v>
+      </c>
+      <c r="J36" s="12">
+        <v>1.9199999999999998E-2</v>
+      </c>
+      <c r="K36" s="13">
+        <f t="shared" si="0"/>
+        <v>2.9117647058823528</v>
+      </c>
+      <c r="L36" s="9">
+        <v>1980</v>
+      </c>
+      <c r="M36" s="10">
+        <v>3960</v>
+      </c>
+      <c r="N36" s="11">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="O36" s="10">
+        <v>3366</v>
+      </c>
+      <c r="P36" s="11">
+        <f t="shared" si="2"/>
+        <v>0.20202020202020202</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C37" s="9">
+        <v>20</v>
+      </c>
+      <c r="D37" s="9">
+        <v>37</v>
+      </c>
+      <c r="E37" s="12">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="F37" s="9">
+        <v>592</v>
+      </c>
+      <c r="G37" s="9">
+        <v>16</v>
+      </c>
+      <c r="H37" s="9">
+        <v>3280</v>
+      </c>
+      <c r="I37" s="9">
+        <v>1</v>
+      </c>
+      <c r="J37" s="12">
+        <v>2.7E-2</v>
+      </c>
+      <c r="K37" s="13">
+        <f t="shared" si="0"/>
+        <v>5.5405405405405403</v>
+      </c>
+      <c r="L37" s="9">
+        <v>3280</v>
+      </c>
+      <c r="M37" s="10">
+        <v>6560</v>
+      </c>
+      <c r="N37" s="11">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="O37" s="10">
+        <v>1600</v>
+      </c>
+      <c r="P37" s="11">
+        <f t="shared" si="2"/>
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" s="9">
+        <v>22</v>
+      </c>
+      <c r="D38" s="9">
+        <v>29</v>
+      </c>
+      <c r="E38" s="12">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="F38" s="9">
+        <v>582</v>
+      </c>
+      <c r="G38" s="9">
+        <v>21</v>
+      </c>
+      <c r="H38" s="9">
+        <v>4840</v>
+      </c>
+      <c r="I38" s="9">
+        <v>2</v>
+      </c>
+      <c r="J38" s="12">
+        <v>6.8900000000000003E-2</v>
+      </c>
+      <c r="K38" s="13">
+        <f t="shared" si="0"/>
+        <v>8.3161512027491415</v>
+      </c>
+      <c r="L38" s="9">
+        <v>1680</v>
+      </c>
+      <c r="M38" s="10">
+        <v>1680</v>
+      </c>
+      <c r="N38" s="11">
+        <f t="shared" si="1"/>
+        <v>2.8809523809523809</v>
+      </c>
+      <c r="O38" s="10">
+        <v>486</v>
+      </c>
+      <c r="P38" s="11">
+        <f t="shared" si="2"/>
+        <v>1.1975308641975309</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="C39" s="9">
+        <v>20</v>
+      </c>
+      <c r="D39" s="9">
+        <v>49</v>
+      </c>
+      <c r="E39" s="12">
+        <v>4.6999999999999993E-3</v>
+      </c>
+      <c r="F39" s="9">
+        <v>580</v>
+      </c>
+      <c r="G39" s="9">
+        <v>12</v>
+      </c>
+      <c r="H39" s="9">
+        <v>2480</v>
+      </c>
+      <c r="I39" s="9">
+        <v>1</v>
+      </c>
+      <c r="J39" s="12">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="K39" s="13">
+        <f t="shared" si="0"/>
+        <v>4.2758620689655169</v>
+      </c>
+      <c r="L39" s="9">
+        <v>0</v>
+      </c>
+      <c r="M39" s="10">
+        <v>7440</v>
+      </c>
+      <c r="N39" s="11">
+        <f t="shared" si="1"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O39" s="10">
+        <v>6324</v>
+      </c>
+      <c r="P39" s="11">
+        <f t="shared" si="2"/>
+        <v>9.1714104996837451E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9">
+        <v>20</v>
+      </c>
+      <c r="D40" s="9">
+        <v>42</v>
+      </c>
+      <c r="E40" s="12">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F40" s="9">
+        <v>569</v>
+      </c>
+      <c r="G40" s="9">
+        <v>14</v>
+      </c>
+      <c r="H40" s="9">
+        <v>0</v>
+      </c>
+      <c r="I40" s="9">
+        <v>0</v>
+      </c>
+      <c r="J40" s="12">
+        <v>0</v>
+      </c>
+      <c r="K40" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L40" s="9">
+        <v>0</v>
+      </c>
+      <c r="M40" s="10"/>
+      <c r="N40" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O40" s="10"/>
+      <c r="P40" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9">
+        <v>20</v>
+      </c>
+      <c r="D41" s="9">
+        <v>51</v>
+      </c>
+      <c r="E41" s="12">
+        <v>1.23E-2</v>
+      </c>
+      <c r="F41" s="9">
+        <v>550</v>
+      </c>
+      <c r="G41" s="9">
+        <v>11</v>
+      </c>
+      <c r="H41" s="9">
+        <v>0</v>
+      </c>
+      <c r="I41" s="9">
+        <v>0</v>
+      </c>
+      <c r="J41" s="12">
+        <v>0</v>
+      </c>
+      <c r="K41" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L41" s="9">
+        <v>0</v>
+      </c>
+      <c r="M41" s="10"/>
+      <c r="N41" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O41" s="10"/>
+      <c r="P41" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C42" s="9">
+        <v>24</v>
+      </c>
+      <c r="D42" s="9">
+        <v>38</v>
+      </c>
+      <c r="E42" s="12">
+        <v>3.7000000000000012E-2</v>
+      </c>
+      <c r="F42" s="9">
+        <v>540</v>
+      </c>
+      <c r="G42" s="9">
+        <v>15</v>
+      </c>
+      <c r="H42" s="9">
+        <v>1480</v>
+      </c>
+      <c r="I42" s="9">
+        <v>1</v>
+      </c>
+      <c r="J42" s="12">
+        <v>2.63E-2</v>
+      </c>
+      <c r="K42" s="13">
+        <f t="shared" si="0"/>
+        <v>2.7407407407407409</v>
+      </c>
+      <c r="L42" s="9">
+        <v>1480</v>
+      </c>
+      <c r="M42" s="10">
+        <v>4440</v>
+      </c>
+      <c r="N42" s="11">
+        <f t="shared" si="1"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O42" s="10">
+        <v>1902</v>
+      </c>
+      <c r="P42" s="11">
+        <f t="shared" si="2"/>
+        <v>0.28391167192429023</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9">
+        <v>20</v>
+      </c>
+      <c r="D43" s="9">
+        <v>48</v>
+      </c>
+      <c r="E43" s="12">
+        <v>7.000000000000001E-4</v>
+      </c>
+      <c r="F43" s="9">
+        <v>540</v>
+      </c>
+      <c r="G43" s="9">
+        <v>12</v>
+      </c>
+      <c r="H43" s="9">
+        <v>0</v>
+      </c>
+      <c r="I43" s="9">
+        <v>0</v>
+      </c>
+      <c r="J43" s="12">
+        <v>0</v>
+      </c>
+      <c r="K43" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L43" s="9">
+        <v>0</v>
+      </c>
+      <c r="M43" s="10"/>
+      <c r="N43" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O43" s="10"/>
+      <c r="P43" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9">
+        <v>22</v>
+      </c>
+      <c r="D44" s="9">
+        <v>25</v>
+      </c>
+      <c r="E44" s="12">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="F44" s="9">
+        <v>532</v>
+      </c>
+      <c r="G44" s="9">
+        <v>22</v>
+      </c>
+      <c r="H44" s="9">
+        <v>0</v>
+      </c>
+      <c r="I44" s="9">
+        <v>0</v>
+      </c>
+      <c r="J44" s="12">
+        <v>0</v>
+      </c>
+      <c r="K44" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L44" s="9">
+        <v>0</v>
+      </c>
+      <c r="M44" s="10"/>
+      <c r="N44" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O44" s="10"/>
+      <c r="P44" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45" s="9">
+        <v>22</v>
+      </c>
+      <c r="D45" s="9">
+        <v>24</v>
+      </c>
+      <c r="E45" s="12">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="F45" s="9">
+        <v>522</v>
+      </c>
+      <c r="G45" s="9">
+        <v>22</v>
+      </c>
+      <c r="H45" s="9">
+        <v>2380</v>
+      </c>
+      <c r="I45" s="9">
+        <v>1</v>
+      </c>
+      <c r="J45" s="12">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="K45" s="13">
+        <f t="shared" ref="K45:K76" si="3">IF(F45=0,"",H45/F45)</f>
+        <v>4.5593869731800769</v>
+      </c>
+      <c r="L45" s="9">
+        <v>0</v>
+      </c>
+      <c r="M45" s="10">
+        <v>4760</v>
+      </c>
+      <c r="N45" s="11">
+        <f t="shared" ref="N45:N76" si="4">IF(OR(M45="",M45=0),"",H45/M45)</f>
+        <v>0.5</v>
+      </c>
+      <c r="O45" s="10">
+        <v>1766</v>
+      </c>
+      <c r="P45" s="11">
+        <f t="shared" ref="P45:P76" si="5">IF(OR(O45="",O45=0),"",F45/O45)</f>
+        <v>0.29558323895809741</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" s="9">
+        <v>27</v>
+      </c>
+      <c r="D46" s="9">
+        <v>34</v>
+      </c>
+      <c r="E46" s="12">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="F46" s="9">
+        <v>498</v>
+      </c>
+      <c r="G46" s="9">
+        <v>15</v>
+      </c>
+      <c r="H46" s="9">
+        <v>2180</v>
+      </c>
+      <c r="I46" s="9">
+        <v>1</v>
+      </c>
+      <c r="J46" s="12">
+        <v>2.9399999999999999E-2</v>
+      </c>
+      <c r="K46" s="13">
+        <f t="shared" si="3"/>
+        <v>4.3775100401606428</v>
+      </c>
+      <c r="L46" s="9">
+        <v>2180</v>
+      </c>
+      <c r="M46" s="10">
+        <v>6540</v>
+      </c>
+      <c r="N46" s="11">
+        <f t="shared" si="4"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O46" s="10">
+        <v>2103</v>
+      </c>
+      <c r="P46" s="11">
+        <f t="shared" si="5"/>
+        <v>0.23680456490727533</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C47" s="9">
+        <v>20</v>
+      </c>
+      <c r="D47" s="9">
+        <v>35</v>
+      </c>
+      <c r="E47" s="12">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="F47" s="9">
+        <v>470</v>
+      </c>
+      <c r="G47" s="9">
+        <v>14</v>
+      </c>
+      <c r="H47" s="9">
+        <v>0</v>
+      </c>
+      <c r="I47" s="9">
+        <v>0</v>
+      </c>
+      <c r="J47" s="12">
+        <v>0</v>
+      </c>
+      <c r="K47" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L47" s="9">
+        <v>0</v>
+      </c>
+      <c r="M47" s="10">
+        <v>3160</v>
+      </c>
+      <c r="N47" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O47" s="10">
+        <v>664</v>
+      </c>
+      <c r="P47" s="11">
+        <f t="shared" si="5"/>
+        <v>0.70783132530120485</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9">
+        <v>20</v>
+      </c>
+      <c r="D48" s="9">
+        <v>44</v>
+      </c>
+      <c r="E48" s="12">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="F48" s="9">
+        <v>450</v>
+      </c>
+      <c r="G48" s="9">
+        <v>11</v>
+      </c>
+      <c r="H48" s="9">
+        <v>0</v>
+      </c>
+      <c r="I48" s="9">
+        <v>0</v>
+      </c>
+      <c r="J48" s="12">
+        <v>0</v>
+      </c>
+      <c r="K48" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L48" s="9">
+        <v>0</v>
+      </c>
+      <c r="M48" s="10"/>
+      <c r="N48" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O48" s="10"/>
+      <c r="P48" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="C49" s="9">
+        <v>20</v>
+      </c>
+      <c r="D49" s="9">
+        <v>40</v>
+      </c>
+      <c r="E49" s="12">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="F49" s="9">
+        <v>440</v>
+      </c>
+      <c r="G49" s="9">
+        <v>11</v>
+      </c>
+      <c r="H49" s="9">
+        <v>0</v>
+      </c>
+      <c r="I49" s="9">
+        <v>0</v>
+      </c>
+      <c r="J49" s="12">
+        <v>0</v>
+      </c>
+      <c r="K49" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L49" s="9">
+        <v>0</v>
+      </c>
+      <c r="M49" s="10">
+        <v>4380</v>
+      </c>
+      <c r="N49" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O49" s="10">
+        <v>3723</v>
+      </c>
+      <c r="P49" s="11">
+        <f t="shared" si="5"/>
+        <v>0.11818426000537201</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="C50" s="9">
+        <v>20</v>
+      </c>
+      <c r="D50" s="9">
+        <v>42</v>
+      </c>
+      <c r="E50" s="12">
+        <v>1.09E-2</v>
+      </c>
+      <c r="F50" s="9">
+        <v>440</v>
+      </c>
+      <c r="G50" s="9">
+        <v>11</v>
+      </c>
+      <c r="H50" s="9">
+        <v>0</v>
+      </c>
+      <c r="I50" s="9">
+        <v>0</v>
+      </c>
+      <c r="J50" s="12">
+        <v>0</v>
+      </c>
+      <c r="K50" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L50" s="9">
+        <v>0</v>
+      </c>
+      <c r="M50" s="10">
+        <v>2180</v>
+      </c>
+      <c r="N50" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O50" s="10">
+        <v>723</v>
+      </c>
+      <c r="P50" s="11">
+        <f t="shared" si="5"/>
+        <v>0.60857538035961267</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9">
+        <v>20</v>
+      </c>
+      <c r="D51" s="9">
+        <v>42</v>
+      </c>
+      <c r="E51" s="12">
+        <v>2.3E-3</v>
+      </c>
+      <c r="F51" s="9">
+        <v>430</v>
+      </c>
+      <c r="G51" s="9">
+        <v>11</v>
+      </c>
+      <c r="H51" s="9">
+        <v>0</v>
+      </c>
+      <c r="I51" s="9">
+        <v>0</v>
+      </c>
+      <c r="J51" s="12">
+        <v>0</v>
+      </c>
+      <c r="K51" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L51" s="9">
+        <v>0</v>
+      </c>
+      <c r="M51" s="10"/>
+      <c r="N51" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O51" s="10"/>
+      <c r="P51" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C52" s="9">
+        <v>20</v>
+      </c>
+      <c r="D52" s="9">
+        <v>25</v>
+      </c>
+      <c r="E52" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F52" s="9">
+        <v>412</v>
+      </c>
+      <c r="G52" s="9">
+        <v>17</v>
+      </c>
+      <c r="H52" s="9">
+        <v>0</v>
+      </c>
+      <c r="I52" s="9">
+        <v>0</v>
+      </c>
+      <c r="J52" s="12">
+        <v>0</v>
+      </c>
+      <c r="K52" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L52" s="9">
+        <v>0</v>
+      </c>
+      <c r="M52" s="10">
+        <v>5940</v>
+      </c>
+      <c r="N52" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O52" s="10">
+        <v>2517</v>
+      </c>
+      <c r="P52" s="11">
+        <f t="shared" si="5"/>
+        <v>0.16368692888359157</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C53" s="9">
+        <v>22</v>
+      </c>
+      <c r="D53" s="9">
+        <v>24</v>
+      </c>
+      <c r="E53" s="12">
+        <v>7.000000000000001E-4</v>
+      </c>
+      <c r="F53" s="9">
+        <v>396</v>
+      </c>
+      <c r="G53" s="9">
+        <v>17</v>
+      </c>
+      <c r="H53" s="9">
+        <v>0</v>
+      </c>
+      <c r="I53" s="9">
+        <v>0</v>
+      </c>
+      <c r="J53" s="12">
+        <v>0</v>
+      </c>
+      <c r="K53" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L53" s="9">
+        <v>0</v>
+      </c>
+      <c r="M53" s="10">
+        <v>1280</v>
+      </c>
+      <c r="N53" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O53" s="10">
+        <v>642</v>
+      </c>
+      <c r="P53" s="11">
+        <f t="shared" si="5"/>
+        <v>0.61682242990654201</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="C54" s="9">
+        <v>20</v>
+      </c>
+      <c r="D54" s="9">
+        <v>22</v>
+      </c>
+      <c r="E54" s="12">
+        <v>1.4E-3</v>
+      </c>
+      <c r="F54" s="9">
+        <v>390</v>
+      </c>
+      <c r="G54" s="9">
+        <v>18</v>
+      </c>
+      <c r="H54" s="9">
+        <v>0</v>
+      </c>
+      <c r="I54" s="9">
+        <v>0</v>
+      </c>
+      <c r="J54" s="12">
+        <v>0</v>
+      </c>
+      <c r="K54" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L54" s="9">
+        <v>0</v>
+      </c>
+      <c r="M54" s="10">
+        <v>4960</v>
+      </c>
+      <c r="N54" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O54" s="10">
+        <v>4216</v>
+      </c>
+      <c r="P54" s="11">
+        <f t="shared" si="5"/>
+        <v>9.2504743833017072E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9">
+        <v>20</v>
+      </c>
+      <c r="D55" s="9">
+        <v>31</v>
+      </c>
+      <c r="E55" s="12">
+        <v>2.24E-2</v>
+      </c>
+      <c r="F55" s="9">
+        <v>370</v>
+      </c>
+      <c r="G55" s="9">
+        <v>12</v>
+      </c>
+      <c r="H55" s="9">
+        <v>0</v>
+      </c>
+      <c r="I55" s="9">
+        <v>0</v>
+      </c>
+      <c r="J55" s="12">
+        <v>0</v>
+      </c>
+      <c r="K55" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L55" s="9">
+        <v>0</v>
+      </c>
+      <c r="M55" s="10"/>
+      <c r="N55" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O55" s="10"/>
+      <c r="P55" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9">
+        <v>22</v>
+      </c>
+      <c r="D56" s="9">
+        <v>29</v>
+      </c>
+      <c r="E56" s="12">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="F56" s="9">
+        <v>356</v>
+      </c>
+      <c r="G56" s="9">
+        <v>13</v>
+      </c>
+      <c r="H56" s="9">
+        <v>0</v>
+      </c>
+      <c r="I56" s="9">
+        <v>0</v>
+      </c>
+      <c r="J56" s="12">
+        <v>0</v>
+      </c>
+      <c r="K56" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L56" s="9">
+        <v>0</v>
+      </c>
+      <c r="M56" s="10"/>
+      <c r="N56" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O56" s="10"/>
+      <c r="P56" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9">
+        <v>20</v>
+      </c>
+      <c r="D57" s="9">
+        <v>29</v>
+      </c>
+      <c r="E57" s="12">
+        <v>1.4E-3</v>
+      </c>
+      <c r="F57" s="9">
+        <v>340</v>
+      </c>
+      <c r="G57" s="9">
+        <v>12</v>
+      </c>
+      <c r="H57" s="9">
+        <v>0</v>
+      </c>
+      <c r="I57" s="9">
+        <v>0</v>
+      </c>
+      <c r="J57" s="12">
+        <v>0</v>
+      </c>
+      <c r="K57" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L57" s="9">
+        <v>0</v>
+      </c>
+      <c r="M57" s="10"/>
+      <c r="N57" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O57" s="10"/>
+      <c r="P57" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9">
+        <v>20</v>
+      </c>
+      <c r="D58" s="9">
+        <v>32</v>
+      </c>
+      <c r="E58" s="12">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="F58" s="9">
+        <v>330</v>
+      </c>
+      <c r="G58" s="9">
+        <v>11</v>
+      </c>
+      <c r="H58" s="9">
+        <v>0</v>
+      </c>
+      <c r="I58" s="9">
+        <v>0</v>
+      </c>
+      <c r="J58" s="12">
+        <v>0</v>
+      </c>
+      <c r="K58" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L58" s="9">
+        <v>0</v>
+      </c>
+      <c r="M58" s="10"/>
+      <c r="N58" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O58" s="10"/>
+      <c r="P58" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9">
+        <v>20</v>
+      </c>
+      <c r="D59" s="9">
+        <v>32</v>
+      </c>
+      <c r="E59" s="12">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="F59" s="9">
+        <v>330</v>
+      </c>
+      <c r="G59" s="9">
+        <v>11</v>
+      </c>
+      <c r="H59" s="9">
+        <v>0</v>
+      </c>
+      <c r="I59" s="9">
+        <v>0</v>
+      </c>
+      <c r="J59" s="12">
+        <v>0</v>
+      </c>
+      <c r="K59" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L59" s="9">
+        <v>0</v>
+      </c>
+      <c r="M59" s="10"/>
+      <c r="N59" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O59" s="10"/>
+      <c r="P59" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9">
+        <v>20</v>
+      </c>
+      <c r="D60" s="9">
+        <v>33</v>
+      </c>
+      <c r="E60" s="12">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F60" s="9">
+        <v>330</v>
+      </c>
+      <c r="G60" s="9">
+        <v>10</v>
+      </c>
+      <c r="H60" s="9">
+        <v>0</v>
+      </c>
+      <c r="I60" s="9">
+        <v>0</v>
+      </c>
+      <c r="J60" s="12">
+        <v>0</v>
+      </c>
+      <c r="K60" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L60" s="9">
+        <v>0</v>
+      </c>
+      <c r="M60" s="10"/>
+      <c r="N60" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O60" s="10"/>
+      <c r="P60" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="C61" s="9">
+        <v>20</v>
+      </c>
+      <c r="D61" s="9">
+        <v>23</v>
+      </c>
+      <c r="E61" s="12">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="F61" s="9">
+        <v>323</v>
+      </c>
+      <c r="G61" s="9">
+        <v>15</v>
+      </c>
+      <c r="H61" s="9">
+        <v>0</v>
+      </c>
+      <c r="I61" s="9">
+        <v>0</v>
+      </c>
+      <c r="J61" s="12">
+        <v>0</v>
+      </c>
+      <c r="K61" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L61" s="9">
+        <v>0</v>
+      </c>
+      <c r="M61" s="10">
+        <v>11880</v>
+      </c>
+      <c r="N61" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O61" s="10">
+        <v>10098</v>
+      </c>
+      <c r="P61" s="11">
+        <f t="shared" si="5"/>
+        <v>3.1986531986531987E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16">
+      <c r="A62" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="B62" s="9"/>
+      <c r="C62" s="9">
+        <v>20</v>
+      </c>
+      <c r="D62" s="9">
+        <v>28</v>
+      </c>
+      <c r="E62" s="12">
+        <v>0</v>
+      </c>
+      <c r="F62" s="9">
+        <v>280</v>
+      </c>
+      <c r="G62" s="9">
+        <v>10</v>
+      </c>
+      <c r="H62" s="9">
+        <v>0</v>
+      </c>
+      <c r="I62" s="9">
+        <v>0</v>
+      </c>
+      <c r="J62" s="12">
+        <v>0</v>
+      </c>
+      <c r="K62" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L62" s="9">
+        <v>0</v>
+      </c>
+      <c r="M62" s="10"/>
+      <c r="N62" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O62" s="10"/>
+      <c r="P62" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:16">
+      <c r="A63" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C63" s="9">
+        <v>27</v>
+      </c>
+      <c r="D63" s="9">
+        <v>14</v>
+      </c>
+      <c r="E63" s="12">
+        <v>9.0000000000000011E-3</v>
+      </c>
+      <c r="F63" s="9">
+        <v>280</v>
+      </c>
+      <c r="G63" s="9">
+        <v>20</v>
+      </c>
+      <c r="H63" s="9">
+        <v>0</v>
+      </c>
+      <c r="I63" s="9">
+        <v>0</v>
+      </c>
+      <c r="J63" s="12">
+        <v>0</v>
+      </c>
+      <c r="K63" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L63" s="9">
+        <v>0</v>
+      </c>
+      <c r="M63" s="10">
+        <v>14940</v>
+      </c>
+      <c r="N63" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O63" s="10">
+        <v>4935</v>
+      </c>
+      <c r="P63" s="11">
+        <f t="shared" si="5"/>
+        <v>5.6737588652482268E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16">
+      <c r="A64" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="C64" s="9">
+        <v>20</v>
+      </c>
+      <c r="D64" s="9">
+        <v>16</v>
+      </c>
+      <c r="E64" s="12">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="F64" s="9">
+        <v>243</v>
+      </c>
+      <c r="G64" s="9">
+        <v>16</v>
+      </c>
+      <c r="H64" s="9">
+        <v>0</v>
+      </c>
+      <c r="I64" s="9">
+        <v>0</v>
+      </c>
+      <c r="J64" s="12">
+        <v>0</v>
+      </c>
+      <c r="K64" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L64" s="9">
+        <v>0</v>
+      </c>
+      <c r="M64" s="10">
+        <v>4980</v>
+      </c>
+      <c r="N64" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O64" s="10">
+        <v>4233</v>
+      </c>
+      <c r="P64" s="11">
+        <f t="shared" si="5"/>
+        <v>5.7406094968107724E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16">
+      <c r="A65" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9">
+        <v>20</v>
+      </c>
+      <c r="D65" s="9">
+        <v>22</v>
+      </c>
+      <c r="E65" s="12">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="F65" s="9">
+        <v>230</v>
+      </c>
+      <c r="G65" s="9">
+        <v>11</v>
+      </c>
+      <c r="H65" s="9">
+        <v>0</v>
+      </c>
+      <c r="I65" s="9">
+        <v>0</v>
+      </c>
+      <c r="J65" s="12">
+        <v>0</v>
+      </c>
+      <c r="K65" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L65" s="9">
+        <v>0</v>
+      </c>
+      <c r="M65" s="10"/>
+      <c r="N65" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O65" s="10"/>
+      <c r="P65" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:16">
+      <c r="A66" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="B66" s="9"/>
+      <c r="C66" s="9">
+        <v>22</v>
+      </c>
+      <c r="D66" s="9">
+        <v>19</v>
+      </c>
+      <c r="E66" s="12">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F66" s="9">
+        <v>226</v>
+      </c>
+      <c r="G66" s="9">
+        <v>12</v>
+      </c>
+      <c r="H66" s="9">
+        <v>0</v>
+      </c>
+      <c r="I66" s="9">
+        <v>0</v>
+      </c>
+      <c r="J66" s="12">
+        <v>0</v>
+      </c>
+      <c r="K66" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L66" s="9">
+        <v>0</v>
+      </c>
+      <c r="M66" s="10"/>
+      <c r="N66" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O66" s="10"/>
+      <c r="P66" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:16">
+      <c r="A67" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="C67" s="9">
+        <v>20</v>
+      </c>
+      <c r="D67" s="9">
+        <v>20</v>
+      </c>
+      <c r="E67" s="12">
+        <v>7.000000000000001E-4</v>
+      </c>
+      <c r="F67" s="9">
+        <v>215</v>
+      </c>
+      <c r="G67" s="9">
+        <v>11</v>
+      </c>
+      <c r="H67" s="9">
+        <v>0</v>
+      </c>
+      <c r="I67" s="9">
+        <v>0</v>
+      </c>
+      <c r="J67" s="12">
+        <v>0</v>
+      </c>
+      <c r="K67" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L67" s="9">
+        <v>0</v>
+      </c>
+      <c r="M67" s="10">
+        <v>23940</v>
+      </c>
+      <c r="N67" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O67" s="10">
+        <v>20349</v>
+      </c>
+      <c r="P67" s="11">
+        <f t="shared" si="5"/>
+        <v>1.0565629760676201E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16">
+      <c r="A68" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C68" s="9">
+        <v>20</v>
+      </c>
+      <c r="D68" s="9">
+        <v>14</v>
+      </c>
+      <c r="E68" s="12">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="F68" s="9">
+        <v>200</v>
+      </c>
+      <c r="G68" s="9">
+        <v>15</v>
+      </c>
+      <c r="H68" s="9">
+        <v>0</v>
+      </c>
+      <c r="I68" s="9">
+        <v>0</v>
+      </c>
+      <c r="J68" s="12">
+        <v>0</v>
+      </c>
+      <c r="K68" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L68" s="9">
+        <v>0</v>
+      </c>
+      <c r="M68" s="10">
+        <v>2980</v>
+      </c>
+      <c r="N68" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O68" s="10">
+        <v>797</v>
+      </c>
+      <c r="P68" s="11">
+        <f t="shared" si="5"/>
+        <v>0.25094102885821834</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16">
+      <c r="A69" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="B69" s="9"/>
+      <c r="C69" s="9">
+        <v>20</v>
+      </c>
+      <c r="D69" s="9">
+        <v>19</v>
+      </c>
+      <c r="E69" s="12">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F69" s="9">
+        <v>200</v>
+      </c>
+      <c r="G69" s="9">
+        <v>11</v>
+      </c>
+      <c r="H69" s="9">
+        <v>0</v>
+      </c>
+      <c r="I69" s="9">
+        <v>0</v>
+      </c>
+      <c r="J69" s="12">
+        <v>0</v>
+      </c>
+      <c r="K69" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L69" s="9">
+        <v>0</v>
+      </c>
+      <c r="M69" s="10"/>
+      <c r="N69" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O69" s="10"/>
+      <c r="P69" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:16">
+      <c r="A70" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9">
+        <v>20</v>
+      </c>
+      <c r="D70" s="9">
+        <v>18</v>
+      </c>
+      <c r="E70" s="12">
+        <v>6.9999999999999993E-3</v>
+      </c>
+      <c r="F70" s="9">
+        <v>190</v>
+      </c>
+      <c r="G70" s="9">
+        <v>11</v>
+      </c>
+      <c r="H70" s="9">
+        <v>0</v>
+      </c>
+      <c r="I70" s="9">
+        <v>0</v>
+      </c>
+      <c r="J70" s="12">
+        <v>0</v>
+      </c>
+      <c r="K70" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L70" s="9">
+        <v>0</v>
+      </c>
+      <c r="M70" s="10"/>
+      <c r="N70" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O70" s="10"/>
+      <c r="P70" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:16">
+      <c r="A71" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9">
+        <v>20</v>
+      </c>
+      <c r="D71" s="9">
+        <v>17</v>
+      </c>
+      <c r="E71" s="12">
+        <v>8.1000000000000013E-3</v>
+      </c>
+      <c r="F71" s="9">
+        <v>190</v>
+      </c>
+      <c r="G71" s="9">
+        <v>12</v>
+      </c>
+      <c r="H71" s="9">
+        <v>0</v>
+      </c>
+      <c r="I71" s="9">
+        <v>0</v>
+      </c>
+      <c r="J71" s="12">
+        <v>0</v>
+      </c>
+      <c r="K71" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L71" s="9">
+        <v>0</v>
+      </c>
+      <c r="M71" s="10"/>
+      <c r="N71" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O71" s="10"/>
+      <c r="P71" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:16">
+      <c r="A72" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="B72" s="9"/>
+      <c r="C72" s="9">
+        <v>20</v>
+      </c>
+      <c r="D72" s="9">
+        <v>17</v>
+      </c>
+      <c r="E72" s="12">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="F72" s="9">
+        <v>190</v>
+      </c>
+      <c r="G72" s="9">
+        <v>12</v>
+      </c>
+      <c r="H72" s="9">
+        <v>0</v>
+      </c>
+      <c r="I72" s="9">
+        <v>0</v>
+      </c>
+      <c r="J72" s="12">
+        <v>0</v>
+      </c>
+      <c r="K72" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L72" s="9">
+        <v>0</v>
+      </c>
+      <c r="M72" s="10"/>
+      <c r="N72" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O72" s="10"/>
+      <c r="P72" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:16">
+      <c r="A73" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="B73" s="9"/>
+      <c r="C73" s="9">
+        <v>20</v>
+      </c>
+      <c r="D73" s="9">
+        <v>18</v>
+      </c>
+      <c r="E73" s="12">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="F73" s="9">
+        <v>180</v>
+      </c>
+      <c r="G73" s="9">
+        <v>10</v>
+      </c>
+      <c r="H73" s="9">
+        <v>0</v>
+      </c>
+      <c r="I73" s="9">
+        <v>0</v>
+      </c>
+      <c r="J73" s="12">
+        <v>0</v>
+      </c>
+      <c r="K73" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L73" s="9">
+        <v>0</v>
+      </c>
+      <c r="M73" s="10"/>
+      <c r="N73" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O73" s="10"/>
+      <c r="P73" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:16">
+      <c r="A74" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="B74" s="9"/>
+      <c r="C74" s="9">
+        <v>20</v>
+      </c>
+      <c r="D74" s="9">
+        <v>16</v>
+      </c>
+      <c r="E74" s="12">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="F74" s="9">
+        <v>180</v>
+      </c>
+      <c r="G74" s="9">
+        <v>12</v>
+      </c>
+      <c r="H74" s="9">
+        <v>0</v>
+      </c>
+      <c r="I74" s="9">
+        <v>0</v>
+      </c>
+      <c r="J74" s="12">
+        <v>0</v>
+      </c>
+      <c r="K74" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L74" s="9">
+        <v>0</v>
+      </c>
+      <c r="M74" s="10"/>
+      <c r="N74" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O74" s="10"/>
+      <c r="P74" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:16">
+      <c r="A75" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="B75" s="9"/>
+      <c r="C75" s="9">
+        <v>20</v>
+      </c>
+      <c r="D75" s="9">
+        <v>18</v>
+      </c>
+      <c r="E75" s="12">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="F75" s="9">
+        <v>180</v>
+      </c>
+      <c r="G75" s="9">
+        <v>10</v>
+      </c>
+      <c r="H75" s="9">
+        <v>0</v>
+      </c>
+      <c r="I75" s="9">
+        <v>0</v>
+      </c>
+      <c r="J75" s="12">
+        <v>0</v>
+      </c>
+      <c r="K75" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L75" s="9">
+        <v>0</v>
+      </c>
+      <c r="M75" s="10"/>
+      <c r="N75" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O75" s="10"/>
+      <c r="P75" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:16">
+      <c r="A76" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C76" s="9">
+        <v>20</v>
+      </c>
+      <c r="D76" s="9">
+        <v>14</v>
+      </c>
+      <c r="E76" s="12">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F76" s="9">
+        <v>170</v>
+      </c>
+      <c r="G76" s="9">
+        <v>13</v>
+      </c>
+      <c r="H76" s="9">
+        <v>4218</v>
+      </c>
+      <c r="I76" s="9">
+        <v>1</v>
+      </c>
+      <c r="J76" s="12">
+        <v>7.1399999999999991E-2</v>
+      </c>
+      <c r="K76" s="13">
+        <f t="shared" si="3"/>
+        <v>24.811764705882354</v>
+      </c>
+      <c r="L76" s="9">
+        <v>0</v>
+      </c>
+      <c r="M76" s="10">
+        <v>12654</v>
+      </c>
+      <c r="N76" s="11">
+        <f t="shared" si="4"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O76" s="10">
+        <v>376</v>
+      </c>
+      <c r="P76" s="11">
+        <f t="shared" si="5"/>
+        <v>0.4521276595744681</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16">
+      <c r="A77" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C77" s="9">
+        <v>20</v>
+      </c>
+      <c r="D77" s="9">
+        <v>10</v>
+      </c>
+      <c r="E77" s="12">
+        <v>1E-4</v>
+      </c>
+      <c r="F77" s="9">
+        <v>152</v>
+      </c>
+      <c r="G77" s="9">
+        <v>16</v>
+      </c>
+      <c r="H77" s="9">
+        <v>0</v>
+      </c>
+      <c r="I77" s="9">
+        <v>0</v>
+      </c>
+      <c r="J77" s="12">
+        <v>0</v>
+      </c>
+      <c r="K77" s="13">
+        <f t="shared" ref="K77:K108" si="6">IF(F77=0,"",H77/F77)</f>
+        <v>0</v>
+      </c>
+      <c r="L77" s="9">
+        <v>0</v>
+      </c>
+      <c r="M77" s="10">
+        <v>4218</v>
+      </c>
+      <c r="N77" s="11">
+        <f t="shared" ref="N77:N108" si="7">IF(OR(M77="",M77=0),"",H77/M77)</f>
+        <v>0</v>
+      </c>
+      <c r="O77" s="10">
+        <v>125</v>
+      </c>
+      <c r="P77" s="11">
+        <f t="shared" ref="P77:P108" si="8">IF(OR(O77="",O77=0),"",F77/O77)</f>
+        <v>1.216</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16">
+      <c r="A78" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="C78" s="9">
+        <v>20</v>
+      </c>
+      <c r="D78" s="9">
+        <v>12</v>
+      </c>
+      <c r="E78" s="12">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="F78" s="9">
+        <v>130</v>
+      </c>
+      <c r="G78" s="9">
+        <v>11</v>
+      </c>
+      <c r="H78" s="9">
+        <v>0</v>
+      </c>
+      <c r="I78" s="9">
+        <v>0</v>
+      </c>
+      <c r="J78" s="12">
+        <v>0</v>
+      </c>
+      <c r="K78" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L78" s="9">
+        <v>0</v>
+      </c>
+      <c r="M78" s="10">
+        <v>12540</v>
+      </c>
+      <c r="N78" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O78" s="10">
+        <v>10659</v>
+      </c>
+      <c r="P78" s="11">
+        <f t="shared" si="8"/>
+        <v>1.2196266066235107E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16">
+      <c r="A79" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B79" s="9"/>
+      <c r="C79" s="9">
+        <v>20</v>
+      </c>
+      <c r="D79" s="9">
+        <v>13</v>
+      </c>
+      <c r="E79" s="12">
+        <v>0</v>
+      </c>
+      <c r="F79" s="9">
+        <v>130</v>
+      </c>
+      <c r="G79" s="9">
+        <v>10</v>
+      </c>
+      <c r="H79" s="9">
+        <v>0</v>
+      </c>
+      <c r="I79" s="9">
+        <v>0</v>
+      </c>
+      <c r="J79" s="12">
+        <v>0</v>
+      </c>
+      <c r="K79" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L79" s="9">
+        <v>0</v>
+      </c>
+      <c r="M79" s="10"/>
+      <c r="N79" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O79" s="10"/>
+      <c r="P79" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:16">
+      <c r="A80" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B80" s="9"/>
+      <c r="C80" s="9">
+        <v>20</v>
+      </c>
+      <c r="D80" s="9">
+        <v>9</v>
+      </c>
+      <c r="E80" s="12">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="F80" s="9">
+        <v>120</v>
+      </c>
+      <c r="G80" s="9">
+        <v>14</v>
+      </c>
+      <c r="H80" s="9">
+        <v>0</v>
+      </c>
+      <c r="I80" s="9">
+        <v>0</v>
+      </c>
+      <c r="J80" s="12">
+        <v>0</v>
+      </c>
+      <c r="K80" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L80" s="9">
+        <v>0</v>
+      </c>
+      <c r="M80" s="10"/>
+      <c r="N80" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O80" s="10"/>
+      <c r="P80" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:16">
+      <c r="A81" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C81" s="9">
+        <v>20</v>
+      </c>
+      <c r="D81" s="9">
+        <v>11</v>
+      </c>
+      <c r="E81" s="12">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="F81" s="9">
+        <v>110</v>
+      </c>
+      <c r="G81" s="9">
+        <v>10</v>
+      </c>
+      <c r="H81" s="9">
+        <v>0</v>
+      </c>
+      <c r="I81" s="9">
+        <v>0</v>
+      </c>
+      <c r="J81" s="12">
+        <v>0</v>
+      </c>
+      <c r="K81" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L81" s="9">
+        <v>0</v>
+      </c>
+      <c r="M81" s="10">
+        <v>5360</v>
+      </c>
+      <c r="N81" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O81" s="10">
+        <v>4556</v>
+      </c>
+      <c r="P81" s="11">
+        <f t="shared" si="8"/>
+        <v>2.4143985952589993E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16">
+      <c r="A82" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C82" s="9">
+        <v>20</v>
+      </c>
+      <c r="D82" s="9">
+        <v>11</v>
+      </c>
+      <c r="E82" s="12">
+        <v>2E-3</v>
+      </c>
+      <c r="F82" s="9">
+        <v>110</v>
+      </c>
+      <c r="G82" s="9">
+        <v>10</v>
+      </c>
+      <c r="H82" s="9">
+        <v>0</v>
+      </c>
+      <c r="I82" s="9">
+        <v>0</v>
+      </c>
+      <c r="J82" s="12">
+        <v>0</v>
+      </c>
+      <c r="K82" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L82" s="9">
+        <v>0</v>
+      </c>
+      <c r="M82" s="10">
+        <v>18360</v>
+      </c>
+      <c r="N82" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O82" s="10">
+        <v>3646</v>
+      </c>
+      <c r="P82" s="11">
+        <f t="shared" si="8"/>
+        <v>3.0170049369171694E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16">
+      <c r="A83" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C83" s="9">
+        <v>20</v>
+      </c>
+      <c r="D83" s="9">
+        <v>5</v>
+      </c>
+      <c r="E83" s="12">
+        <v>2.3E-3</v>
+      </c>
+      <c r="F83" s="9">
+        <v>100</v>
+      </c>
+      <c r="G83" s="9">
+        <v>20</v>
+      </c>
+      <c r="H83" s="9">
+        <v>0</v>
+      </c>
+      <c r="I83" s="9">
+        <v>0</v>
+      </c>
+      <c r="J83" s="12">
+        <v>0</v>
+      </c>
+      <c r="K83" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L83" s="9">
+        <v>0</v>
+      </c>
+      <c r="M83" s="10">
+        <v>1280</v>
+      </c>
+      <c r="N83" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O83" s="10">
+        <v>650</v>
+      </c>
+      <c r="P83" s="11">
+        <f t="shared" si="8"/>
+        <v>0.15384615384615385</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16">
+      <c r="A84" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B84" s="9"/>
+      <c r="C84" s="9">
+        <v>20</v>
+      </c>
+      <c r="D84" s="9">
+        <v>5</v>
+      </c>
+      <c r="E84" s="12">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="F84" s="9">
+        <v>96</v>
+      </c>
+      <c r="G84" s="9">
+        <v>20</v>
+      </c>
+      <c r="H84" s="9">
+        <v>0</v>
+      </c>
+      <c r="I84" s="9">
+        <v>0</v>
+      </c>
+      <c r="J84" s="12">
+        <v>0</v>
+      </c>
+      <c r="K84" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L84" s="9">
+        <v>0</v>
+      </c>
+      <c r="M84" s="10"/>
+      <c r="N84" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O84" s="10"/>
+      <c r="P84" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:16">
+      <c r="A85" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B85" s="9"/>
+      <c r="C85" s="9">
+        <v>24</v>
+      </c>
+      <c r="D85" s="9">
+        <v>8</v>
+      </c>
+      <c r="E85" s="12">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="F85" s="9">
+        <v>94</v>
+      </c>
+      <c r="G85" s="9">
+        <v>12</v>
+      </c>
+      <c r="H85" s="9">
+        <v>0</v>
+      </c>
+      <c r="I85" s="9">
+        <v>0</v>
+      </c>
+      <c r="J85" s="12">
+        <v>0</v>
+      </c>
+      <c r="K85" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L85" s="9">
+        <v>0</v>
+      </c>
+      <c r="M85" s="10"/>
+      <c r="N85" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O85" s="10"/>
+      <c r="P85" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:16">
+      <c r="A86" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B86" s="9"/>
+      <c r="C86" s="9">
+        <v>20</v>
+      </c>
+      <c r="D86" s="9">
+        <v>4</v>
+      </c>
+      <c r="E86" s="12">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="F86" s="9">
+        <v>80</v>
+      </c>
+      <c r="G86" s="9">
+        <v>20</v>
+      </c>
+      <c r="H86" s="9">
+        <v>0</v>
+      </c>
+      <c r="I86" s="9">
+        <v>0</v>
+      </c>
+      <c r="J86" s="12">
+        <v>0</v>
+      </c>
+      <c r="K86" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L86" s="9">
+        <v>0</v>
+      </c>
+      <c r="M86" s="10"/>
+      <c r="N86" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O86" s="10"/>
+      <c r="P86" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:16">
+      <c r="A87" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B87" s="9"/>
+      <c r="C87" s="9">
+        <v>20</v>
+      </c>
+      <c r="D87" s="9">
+        <v>4</v>
+      </c>
+      <c r="E87" s="12">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="F87" s="9">
+        <v>73</v>
+      </c>
+      <c r="G87" s="9">
+        <v>19</v>
+      </c>
+      <c r="H87" s="9">
+        <v>0</v>
+      </c>
+      <c r="I87" s="9">
+        <v>0</v>
+      </c>
+      <c r="J87" s="12">
+        <v>0</v>
+      </c>
+      <c r="K87" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L87" s="9">
+        <v>0</v>
+      </c>
+      <c r="M87" s="10"/>
+      <c r="N87" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O87" s="10"/>
+      <c r="P87" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:16">
+      <c r="A88" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="C88" s="9">
+        <v>20</v>
+      </c>
+      <c r="D88" s="9">
+        <v>6</v>
+      </c>
+      <c r="E88" s="12">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F88" s="9">
+        <v>72</v>
+      </c>
+      <c r="G88" s="9">
+        <v>12</v>
+      </c>
+      <c r="H88" s="9">
+        <v>0</v>
+      </c>
+      <c r="I88" s="9">
+        <v>0</v>
+      </c>
+      <c r="J88" s="12">
+        <v>0</v>
+      </c>
+      <c r="K88" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L88" s="9">
+        <v>0</v>
+      </c>
+      <c r="M88" s="10">
+        <v>2780</v>
+      </c>
+      <c r="N88" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O88" s="10">
+        <v>1251</v>
+      </c>
+      <c r="P88" s="11">
+        <f t="shared" si="8"/>
+        <v>5.7553956834532377E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16">
+      <c r="A89" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B89" s="9"/>
+      <c r="C89" s="9">
+        <v>20</v>
+      </c>
+      <c r="D89" s="9">
+        <v>4</v>
+      </c>
+      <c r="E89" s="12">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="F89" s="9">
+        <v>70</v>
+      </c>
+      <c r="G89" s="9">
+        <v>18</v>
+      </c>
+      <c r="H89" s="9">
+        <v>0</v>
+      </c>
+      <c r="I89" s="9">
+        <v>0</v>
+      </c>
+      <c r="J89" s="12">
+        <v>0</v>
+      </c>
+      <c r="K89" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L89" s="9">
+        <v>0</v>
+      </c>
+      <c r="M89" s="10"/>
+      <c r="N89" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O89" s="10"/>
+      <c r="P89" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:16">
+      <c r="A90" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B90" s="9"/>
+      <c r="C90" s="9">
+        <v>20</v>
+      </c>
+      <c r="D90" s="9">
+        <v>4</v>
+      </c>
+      <c r="E90" s="12">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F90" s="9">
+        <v>70</v>
+      </c>
+      <c r="G90" s="9">
+        <v>18</v>
+      </c>
+      <c r="H90" s="9">
+        <v>0</v>
+      </c>
+      <c r="I90" s="9">
+        <v>0</v>
+      </c>
+      <c r="J90" s="12">
+        <v>0</v>
+      </c>
+      <c r="K90" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L90" s="9">
+        <v>0</v>
+      </c>
+      <c r="M90" s="10"/>
+      <c r="N90" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O90" s="10"/>
+      <c r="P90" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="1:16">
+      <c r="A91" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B91" s="9"/>
+      <c r="C91" s="9">
+        <v>20</v>
+      </c>
+      <c r="D91" s="9">
+        <v>4</v>
+      </c>
+      <c r="E91" s="12">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="F91" s="9">
+        <v>69</v>
+      </c>
+      <c r="G91" s="9">
+        <v>18</v>
+      </c>
+      <c r="H91" s="9">
+        <v>0</v>
+      </c>
+      <c r="I91" s="9">
+        <v>0</v>
+      </c>
+      <c r="J91" s="12">
+        <v>0</v>
+      </c>
+      <c r="K91" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L91" s="9">
+        <v>0</v>
+      </c>
+      <c r="M91" s="10"/>
+      <c r="N91" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O91" s="10"/>
+      <c r="P91" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:16">
+      <c r="A92" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="C92" s="9">
+        <v>20</v>
+      </c>
+      <c r="D92" s="9">
+        <v>4</v>
+      </c>
+      <c r="E92" s="12">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="F92" s="9">
+        <v>64</v>
+      </c>
+      <c r="G92" s="9">
+        <v>16</v>
+      </c>
+      <c r="H92" s="9">
+        <v>9160</v>
+      </c>
+      <c r="I92" s="9">
+        <v>2</v>
+      </c>
+      <c r="J92" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="K92" s="13">
+        <f t="shared" si="6"/>
+        <v>143.125</v>
+      </c>
+      <c r="L92" s="9">
+        <v>0</v>
+      </c>
+      <c r="M92" s="10">
+        <v>9160</v>
+      </c>
+      <c r="N92" s="11">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="O92" s="10">
+        <v>7786</v>
+      </c>
+      <c r="P92" s="11">
+        <f t="shared" si="8"/>
+        <v>8.2198818391985614E-3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16">
+      <c r="A93" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="B93" s="9"/>
+      <c r="C93" s="9">
+        <v>20</v>
+      </c>
+      <c r="D93" s="9">
+        <v>4</v>
+      </c>
+      <c r="E93" s="12">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="F93" s="9">
+        <v>60</v>
+      </c>
+      <c r="G93" s="9">
+        <v>15</v>
+      </c>
+      <c r="H93" s="9">
+        <v>0</v>
+      </c>
+      <c r="I93" s="9">
+        <v>0</v>
+      </c>
+      <c r="J93" s="12">
+        <v>0</v>
+      </c>
+      <c r="K93" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L93" s="9">
+        <v>0</v>
+      </c>
+      <c r="M93" s="10"/>
+      <c r="N93" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O93" s="10"/>
+      <c r="P93" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="1:16">
+      <c r="A94" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B94" s="9"/>
+      <c r="C94" s="9">
+        <v>20</v>
+      </c>
+      <c r="D94" s="9">
+        <v>3</v>
+      </c>
+      <c r="E94" s="12">
+        <v>2E-3</v>
+      </c>
+      <c r="F94" s="9">
+        <v>60</v>
+      </c>
+      <c r="G94" s="9">
+        <v>20</v>
+      </c>
+      <c r="H94" s="9">
+        <v>0</v>
+      </c>
+      <c r="I94" s="9">
+        <v>0</v>
+      </c>
+      <c r="J94" s="12">
+        <v>0</v>
+      </c>
+      <c r="K94" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L94" s="9">
+        <v>0</v>
+      </c>
+      <c r="M94" s="10"/>
+      <c r="N94" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O94" s="10"/>
+      <c r="P94" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="1:16">
+      <c r="A95" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B95" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C95" s="9">
+        <v>20</v>
+      </c>
+      <c r="D95" s="9">
+        <v>6</v>
+      </c>
+      <c r="E95" s="12">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F95" s="9">
+        <v>60</v>
+      </c>
+      <c r="G95" s="9">
+        <v>10</v>
+      </c>
+      <c r="H95" s="9">
+        <v>0</v>
+      </c>
+      <c r="I95" s="9">
+        <v>0</v>
+      </c>
+      <c r="J95" s="12">
+        <v>0</v>
+      </c>
+      <c r="K95" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L95" s="9">
+        <v>0</v>
+      </c>
+      <c r="M95" s="10">
+        <v>4960</v>
+      </c>
+      <c r="N95" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O95" s="10">
+        <v>1504</v>
+      </c>
+      <c r="P95" s="11">
+        <f t="shared" si="8"/>
+        <v>3.9893617021276598E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16">
+      <c r="A96" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="B96" s="9"/>
+      <c r="C96" s="9">
+        <v>20</v>
+      </c>
+      <c r="D96" s="9">
+        <v>3</v>
+      </c>
+      <c r="E96" s="12">
+        <v>1.32E-2</v>
+      </c>
+      <c r="F96" s="9">
+        <v>60</v>
+      </c>
+      <c r="G96" s="9">
+        <v>20</v>
+      </c>
+      <c r="H96" s="9">
+        <v>0</v>
+      </c>
+      <c r="I96" s="9">
+        <v>0</v>
+      </c>
+      <c r="J96" s="12">
+        <v>0</v>
+      </c>
+      <c r="K96" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L96" s="9">
+        <v>0</v>
+      </c>
+      <c r="M96" s="10"/>
+      <c r="N96" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O96" s="10"/>
+      <c r="P96" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="1:16">
+      <c r="A97" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="C97" s="9">
+        <v>20</v>
+      </c>
+      <c r="D97" s="9">
+        <v>3</v>
+      </c>
+      <c r="E97" s="12">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F97" s="9">
+        <v>60</v>
+      </c>
+      <c r="G97" s="9">
+        <v>20</v>
+      </c>
+      <c r="H97" s="9">
+        <v>0</v>
+      </c>
+      <c r="I97" s="9">
+        <v>0</v>
+      </c>
+      <c r="J97" s="12">
+        <v>0</v>
+      </c>
+      <c r="K97" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L97" s="9">
+        <v>0</v>
+      </c>
+      <c r="M97" s="10">
+        <v>3480</v>
+      </c>
+      <c r="N97" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O97" s="10">
+        <v>-6803</v>
+      </c>
+      <c r="P97" s="11">
+        <f t="shared" si="8"/>
+        <v>-8.8196383948258121E-3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16">
+      <c r="A98" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B98" s="9"/>
+      <c r="C98" s="9">
+        <v>20</v>
+      </c>
+      <c r="D98" s="9">
+        <v>3</v>
+      </c>
+      <c r="E98" s="12">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="F98" s="9">
+        <v>60</v>
+      </c>
+      <c r="G98" s="9">
+        <v>20</v>
+      </c>
+      <c r="H98" s="9">
+        <v>0</v>
+      </c>
+      <c r="I98" s="9">
+        <v>0</v>
+      </c>
+      <c r="J98" s="12">
+        <v>0</v>
+      </c>
+      <c r="K98" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L98" s="9">
+        <v>0</v>
+      </c>
+      <c r="M98" s="10"/>
+      <c r="N98" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O98" s="10"/>
+      <c r="P98" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="1:16">
+      <c r="A99" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B99" s="9"/>
+      <c r="C99" s="9">
+        <v>20</v>
+      </c>
+      <c r="D99" s="9">
+        <v>5</v>
+      </c>
+      <c r="E99" s="12">
+        <v>1E-4</v>
+      </c>
+      <c r="F99" s="9">
+        <v>60</v>
+      </c>
+      <c r="G99" s="9">
+        <v>12</v>
+      </c>
+      <c r="H99" s="9">
+        <v>0</v>
+      </c>
+      <c r="I99" s="9">
+        <v>0</v>
+      </c>
+      <c r="J99" s="12">
+        <v>0</v>
+      </c>
+      <c r="K99" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L99" s="9">
+        <v>0</v>
+      </c>
+      <c r="M99" s="10"/>
+      <c r="N99" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O99" s="10"/>
+      <c r="P99" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:16">
+      <c r="A100" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="B100" s="9"/>
+      <c r="C100" s="9">
+        <v>20</v>
+      </c>
+      <c r="D100" s="9">
+        <v>3</v>
+      </c>
+      <c r="E100" s="12">
+        <v>2.29E-2</v>
+      </c>
+      <c r="F100" s="9">
+        <v>60</v>
+      </c>
+      <c r="G100" s="9">
+        <v>20</v>
+      </c>
+      <c r="H100" s="9">
+        <v>0</v>
+      </c>
+      <c r="I100" s="9">
+        <v>0</v>
+      </c>
+      <c r="J100" s="12">
+        <v>0</v>
+      </c>
+      <c r="K100" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L100" s="9">
+        <v>0</v>
+      </c>
+      <c r="M100" s="10"/>
+      <c r="N100" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O100" s="10"/>
+      <c r="P100" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="1:16">
+      <c r="A101" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="C101" s="9">
+        <v>20</v>
+      </c>
+      <c r="D101" s="9">
+        <v>4</v>
+      </c>
+      <c r="E101" s="12">
+        <v>1E-4</v>
+      </c>
+      <c r="F101" s="9">
+        <v>52</v>
+      </c>
+      <c r="G101" s="9">
+        <v>13</v>
+      </c>
+      <c r="H101" s="9">
+        <v>0</v>
+      </c>
+      <c r="I101" s="9">
+        <v>0</v>
+      </c>
+      <c r="J101" s="12">
+        <v>0</v>
+      </c>
+      <c r="K101" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L101" s="9">
+        <v>0</v>
+      </c>
+      <c r="M101" s="10">
+        <v>2980</v>
+      </c>
+      <c r="N101" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O101" s="10">
+        <v>797</v>
+      </c>
+      <c r="P101" s="11">
+        <f t="shared" si="8"/>
+        <v>6.5244667503136761E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16">
+      <c r="A102" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="B102" s="9"/>
+      <c r="C102" s="9">
+        <v>20</v>
+      </c>
+      <c r="D102" s="9">
+        <v>5</v>
+      </c>
+      <c r="E102" s="12">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="F102" s="9">
+        <v>50</v>
+      </c>
+      <c r="G102" s="9">
+        <v>10</v>
+      </c>
+      <c r="H102" s="9">
+        <v>0</v>
+      </c>
+      <c r="I102" s="9">
+        <v>0</v>
+      </c>
+      <c r="J102" s="12">
+        <v>0</v>
+      </c>
+      <c r="K102" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L102" s="9">
+        <v>0</v>
+      </c>
+      <c r="M102" s="10"/>
+      <c r="N102" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O102" s="10"/>
+      <c r="P102" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="1:16">
+      <c r="A103" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C103" s="9">
+        <v>20</v>
+      </c>
+      <c r="D103" s="9">
+        <v>4</v>
+      </c>
+      <c r="E103" s="12">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="F103" s="9">
+        <v>50</v>
+      </c>
+      <c r="G103" s="9">
+        <v>13</v>
+      </c>
+      <c r="H103" s="9">
+        <v>0</v>
+      </c>
+      <c r="I103" s="9">
+        <v>0</v>
+      </c>
+      <c r="J103" s="12">
+        <v>0</v>
+      </c>
+      <c r="K103" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L103" s="9">
+        <v>0</v>
+      </c>
+      <c r="M103" s="10">
+        <v>74280</v>
+      </c>
+      <c r="N103" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O103" s="10">
+        <v>31938</v>
+      </c>
+      <c r="P103" s="11">
+        <f t="shared" si="8"/>
+        <v>1.5655332206149415E-3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16">
+      <c r="A104" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B104" s="9"/>
+      <c r="C104" s="9">
+        <v>20</v>
+      </c>
+      <c r="D104" s="9">
+        <v>3</v>
+      </c>
+      <c r="E104" s="12">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="F104" s="9">
+        <v>50</v>
+      </c>
+      <c r="G104" s="9">
+        <v>17</v>
+      </c>
+      <c r="H104" s="9">
+        <v>0</v>
+      </c>
+      <c r="I104" s="9">
+        <v>0</v>
+      </c>
+      <c r="J104" s="12">
+        <v>0</v>
+      </c>
+      <c r="K104" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L104" s="9">
+        <v>0</v>
+      </c>
+      <c r="M104" s="10"/>
+      <c r="N104" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O104" s="10"/>
+      <c r="P104" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="1:16">
+      <c r="A105" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B105" s="9"/>
+      <c r="C105" s="9">
+        <v>20</v>
+      </c>
+      <c r="D105" s="9">
+        <v>5</v>
+      </c>
+      <c r="E105" s="12">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F105" s="9">
+        <v>50</v>
+      </c>
+      <c r="G105" s="9">
+        <v>10</v>
+      </c>
+      <c r="H105" s="9">
+        <v>0</v>
+      </c>
+      <c r="I105" s="9">
+        <v>0</v>
+      </c>
+      <c r="J105" s="12">
+        <v>0</v>
+      </c>
+      <c r="K105" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L105" s="9">
+        <v>0</v>
+      </c>
+      <c r="M105" s="10"/>
+      <c r="N105" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O105" s="10"/>
+      <c r="P105" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:16">
+      <c r="A106" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="C106" s="9">
+        <v>20</v>
+      </c>
+      <c r="D106" s="9">
+        <v>4</v>
+      </c>
+      <c r="E106" s="12">
+        <v>1.8E-3</v>
+      </c>
+      <c r="F106" s="9">
+        <v>50</v>
+      </c>
+      <c r="G106" s="9">
+        <v>13</v>
+      </c>
+      <c r="H106" s="9">
+        <v>0</v>
+      </c>
+      <c r="I106" s="9">
+        <v>0</v>
+      </c>
+      <c r="J106" s="12">
+        <v>0</v>
+      </c>
+      <c r="K106" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L106" s="9">
+        <v>0</v>
+      </c>
+      <c r="M106" s="10">
+        <v>3480</v>
+      </c>
+      <c r="N106" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O106" s="10">
+        <v>1398</v>
+      </c>
+      <c r="P106" s="11">
+        <f t="shared" si="8"/>
+        <v>3.5765379113018601E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16">
+      <c r="A107" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="B107" s="9"/>
+      <c r="C107" s="9">
+        <v>20</v>
+      </c>
+      <c r="D107" s="9">
+        <v>4</v>
+      </c>
+      <c r="E107" s="12">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="F107" s="9">
+        <v>43</v>
+      </c>
+      <c r="G107" s="9">
+        <v>11</v>
+      </c>
+      <c r="H107" s="9">
+        <v>0</v>
+      </c>
+      <c r="I107" s="9">
+        <v>0</v>
+      </c>
+      <c r="J107" s="12">
+        <v>0</v>
+      </c>
+      <c r="K107" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L107" s="9">
+        <v>0</v>
+      </c>
+      <c r="M107" s="10"/>
+      <c r="N107" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O107" s="10"/>
+      <c r="P107" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="108" spans="1:16">
+      <c r="A108" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B108" s="9"/>
+      <c r="C108" s="9">
+        <v>20</v>
+      </c>
+      <c r="D108" s="9">
+        <v>2</v>
+      </c>
+      <c r="E108" s="12">
+        <v>1E-4</v>
+      </c>
+      <c r="F108" s="9">
+        <v>40</v>
+      </c>
+      <c r="G108" s="9">
+        <v>20</v>
+      </c>
+      <c r="H108" s="9">
+        <v>0</v>
+      </c>
+      <c r="I108" s="9">
+        <v>0</v>
+      </c>
+      <c r="J108" s="12">
+        <v>0</v>
+      </c>
+      <c r="K108" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L108" s="9">
+        <v>0</v>
+      </c>
+      <c r="M108" s="10"/>
+      <c r="N108" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O108" s="10"/>
+      <c r="P108" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="109" spans="1:16">
+      <c r="A109" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B109" s="9"/>
+      <c r="C109" s="9">
+        <v>20</v>
+      </c>
+      <c r="D109" s="9">
+        <v>2</v>
+      </c>
+      <c r="E109" s="12">
+        <v>6.4500000000000002E-2</v>
+      </c>
+      <c r="F109" s="9">
+        <v>40</v>
+      </c>
+      <c r="G109" s="9">
+        <v>20</v>
+      </c>
+      <c r="H109" s="9">
+        <v>0</v>
+      </c>
+      <c r="I109" s="9">
+        <v>0</v>
+      </c>
+      <c r="J109" s="12">
+        <v>0</v>
+      </c>
+      <c r="K109" s="13">
+        <f t="shared" ref="K109:K135" si="9">IF(F109=0,"",H109/F109)</f>
+        <v>0</v>
+      </c>
+      <c r="L109" s="9">
+        <v>0</v>
+      </c>
+      <c r="M109" s="10"/>
+      <c r="N109" s="11" t="str">
+        <f t="shared" ref="N109:N140" si="10">IF(OR(M109="",M109=0),"",H109/M109)</f>
+        <v/>
+      </c>
+      <c r="O109" s="10"/>
+      <c r="P109" s="11" t="str">
+        <f t="shared" ref="P109:P140" si="11">IF(OR(O109="",O109=0),"",F109/O109)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="1:16">
+      <c r="A110" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="C110" s="9">
+        <v>20</v>
+      </c>
+      <c r="D110" s="9">
+        <v>2</v>
+      </c>
+      <c r="E110" s="12">
+        <v>0.14280000000000001</v>
+      </c>
+      <c r="F110" s="9">
+        <v>40</v>
+      </c>
+      <c r="G110" s="9">
+        <v>20</v>
+      </c>
+      <c r="H110" s="9">
+        <v>0</v>
+      </c>
+      <c r="I110" s="9">
+        <v>0</v>
+      </c>
+      <c r="J110" s="12">
+        <v>0</v>
+      </c>
+      <c r="K110" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L110" s="9">
+        <v>0</v>
+      </c>
+      <c r="M110" s="10">
+        <v>2560</v>
+      </c>
+      <c r="N110" s="11">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="O110" s="10">
+        <v>616</v>
+      </c>
+      <c r="P110" s="11">
+        <f t="shared" si="11"/>
+        <v>6.4935064935064929E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16">
+      <c r="A111" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="C111" s="9">
+        <v>20</v>
+      </c>
+      <c r="D111" s="9">
+        <v>4</v>
+      </c>
+      <c r="E111" s="12">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="F111" s="9">
+        <v>40</v>
+      </c>
+      <c r="G111" s="9">
+        <v>10</v>
+      </c>
+      <c r="H111" s="9">
+        <v>0</v>
+      </c>
+      <c r="I111" s="9">
+        <v>0</v>
+      </c>
+      <c r="J111" s="12">
+        <v>0</v>
+      </c>
+      <c r="K111" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L111" s="9">
+        <v>0</v>
+      </c>
+      <c r="M111" s="10">
+        <v>4580</v>
+      </c>
+      <c r="N111" s="11">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="O111" s="10">
+        <v>2133</v>
+      </c>
+      <c r="P111" s="11">
+        <f t="shared" si="11"/>
+        <v>1.875293014533521E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16">
+      <c r="A112" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B112" s="9"/>
+      <c r="C112" s="9">
+        <v>20</v>
+      </c>
+      <c r="D112" s="9">
+        <v>3</v>
+      </c>
+      <c r="E112" s="12">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F112" s="9">
+        <v>40</v>
+      </c>
+      <c r="G112" s="9">
+        <v>14</v>
+      </c>
+      <c r="H112" s="9">
+        <v>0</v>
+      </c>
+      <c r="I112" s="9">
+        <v>0</v>
+      </c>
+      <c r="J112" s="12">
+        <v>0</v>
+      </c>
+      <c r="K112" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L112" s="9">
+        <v>0</v>
+      </c>
+      <c r="M112" s="10"/>
+      <c r="N112" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O112" s="10"/>
+      <c r="P112" s="11" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="1:16">
+      <c r="A113" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B113" s="9"/>
+      <c r="C113" s="9">
+        <v>20</v>
+      </c>
+      <c r="D113" s="9">
+        <v>2</v>
+      </c>
+      <c r="E113" s="12">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="F113" s="9">
+        <v>30</v>
+      </c>
+      <c r="G113" s="9">
+        <v>15</v>
+      </c>
+      <c r="H113" s="9">
+        <v>0</v>
+      </c>
+      <c r="I113" s="9">
+        <v>0</v>
+      </c>
+      <c r="J113" s="12">
+        <v>0</v>
+      </c>
+      <c r="K113" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L113" s="9">
+        <v>0</v>
+      </c>
+      <c r="M113" s="10"/>
+      <c r="N113" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O113" s="10"/>
+      <c r="P113" s="11" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="1:16">
+      <c r="A114" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B114" s="9"/>
+      <c r="C114" s="9">
+        <v>20</v>
+      </c>
+      <c r="D114" s="9">
+        <v>3</v>
+      </c>
+      <c r="E114" s="12">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="F114" s="9">
+        <v>30</v>
+      </c>
+      <c r="G114" s="9">
+        <v>10</v>
+      </c>
+      <c r="H114" s="9">
+        <v>0</v>
+      </c>
+      <c r="I114" s="9">
+        <v>0</v>
+      </c>
+      <c r="J114" s="12">
+        <v>0</v>
+      </c>
+      <c r="K114" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L114" s="9">
+        <v>0</v>
+      </c>
+      <c r="M114" s="10"/>
+      <c r="N114" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O114" s="10"/>
+      <c r="P114" s="11" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:16">
+      <c r="A115" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="C115" s="9">
+        <v>20</v>
+      </c>
+      <c r="D115" s="9">
+        <v>2</v>
+      </c>
+      <c r="E115" s="12">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F115" s="9">
+        <v>30</v>
+      </c>
+      <c r="G115" s="9">
+        <v>15</v>
+      </c>
+      <c r="H115" s="9">
+        <v>0</v>
+      </c>
+      <c r="I115" s="9">
+        <v>0</v>
+      </c>
+      <c r="J115" s="12">
+        <v>0</v>
+      </c>
+      <c r="K115" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L115" s="9">
+        <v>0</v>
+      </c>
+      <c r="M115" s="10">
+        <v>10480</v>
+      </c>
+      <c r="N115" s="11">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="O115" s="10">
+        <v>8908</v>
+      </c>
+      <c r="P115" s="11">
+        <f t="shared" si="11"/>
+        <v>3.3677593174674448E-3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16">
+      <c r="A116" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B116" s="9"/>
+      <c r="C116" s="9">
+        <v>20</v>
+      </c>
+      <c r="D116" s="9">
+        <v>2</v>
+      </c>
+      <c r="E116" s="12">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="F116" s="9">
+        <v>30</v>
+      </c>
+      <c r="G116" s="9">
+        <v>15</v>
+      </c>
+      <c r="H116" s="9">
+        <v>0</v>
+      </c>
+      <c r="I116" s="9">
+        <v>0</v>
+      </c>
+      <c r="J116" s="12">
+        <v>0</v>
+      </c>
+      <c r="K116" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L116" s="9">
+        <v>0</v>
+      </c>
+      <c r="M116" s="10"/>
+      <c r="N116" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O116" s="10"/>
+      <c r="P116" s="11" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="1:16">
+      <c r="A117" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B117" s="9"/>
+      <c r="C117" s="9">
+        <v>20</v>
+      </c>
+      <c r="D117" s="9">
+        <v>2</v>
+      </c>
+      <c r="E117" s="12">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="F117" s="9">
+        <v>30</v>
+      </c>
+      <c r="G117" s="9">
+        <v>15</v>
+      </c>
+      <c r="H117" s="9">
+        <v>0</v>
+      </c>
+      <c r="I117" s="9">
+        <v>0</v>
+      </c>
+      <c r="J117" s="12">
+        <v>0</v>
+      </c>
+      <c r="K117" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L117" s="9">
+        <v>0</v>
+      </c>
+      <c r="M117" s="10"/>
+      <c r="N117" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O117" s="10"/>
+      <c r="P117" s="11" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:16">
+      <c r="A118" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B118" s="9"/>
+      <c r="C118" s="9">
+        <v>20</v>
+      </c>
+      <c r="D118" s="9">
+        <v>2</v>
+      </c>
+      <c r="E118" s="12">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="F118" s="9">
+        <v>30</v>
+      </c>
+      <c r="G118" s="9">
+        <v>15</v>
+      </c>
+      <c r="H118" s="9">
+        <v>0</v>
+      </c>
+      <c r="I118" s="9">
+        <v>0</v>
+      </c>
+      <c r="J118" s="12">
+        <v>0</v>
+      </c>
+      <c r="K118" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L118" s="9">
+        <v>0</v>
+      </c>
+      <c r="M118" s="10"/>
+      <c r="N118" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O118" s="10"/>
+      <c r="P118" s="11" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="1:16">
+      <c r="A119" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B119" s="9"/>
+      <c r="C119" s="9">
+        <v>20</v>
+      </c>
+      <c r="D119" s="9">
+        <v>1</v>
+      </c>
+      <c r="E119" s="12">
+        <v>2.7E-2</v>
+      </c>
+      <c r="F119" s="9">
+        <v>20</v>
+      </c>
+      <c r="G119" s="9">
+        <v>20</v>
+      </c>
+      <c r="H119" s="9">
+        <v>0</v>
+      </c>
+      <c r="I119" s="9">
+        <v>0</v>
+      </c>
+      <c r="J119" s="12">
+        <v>0</v>
+      </c>
+      <c r="K119" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L119" s="9">
+        <v>0</v>
+      </c>
+      <c r="M119" s="10"/>
+      <c r="N119" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O119" s="10"/>
+      <c r="P119" s="11" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="1:16">
+      <c r="A120" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B120" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C120" s="9">
+        <v>20</v>
+      </c>
+      <c r="D120" s="9">
+        <v>1</v>
+      </c>
+      <c r="E120" s="12">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="F120" s="9">
+        <v>20</v>
+      </c>
+      <c r="G120" s="9">
+        <v>20</v>
+      </c>
+      <c r="H120" s="9">
+        <v>0</v>
+      </c>
+      <c r="I120" s="9">
+        <v>0</v>
+      </c>
+      <c r="J120" s="12">
+        <v>0</v>
+      </c>
+      <c r="K120" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L120" s="9">
+        <v>0</v>
+      </c>
+      <c r="M120" s="10">
+        <v>2580</v>
+      </c>
+      <c r="N120" s="11">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="O120" s="10">
+        <v>609</v>
+      </c>
+      <c r="P120" s="11">
+        <f t="shared" si="11"/>
+        <v>3.2840722495894911E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16">
+      <c r="A121" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="B121" s="9"/>
+      <c r="C121" s="9">
+        <v>20</v>
+      </c>
+      <c r="D121" s="9">
+        <v>1</v>
+      </c>
+      <c r="E121" s="12">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="F121" s="9">
+        <v>20</v>
+      </c>
+      <c r="G121" s="9">
+        <v>20</v>
+      </c>
+      <c r="H121" s="9">
+        <v>0</v>
+      </c>
+      <c r="I121" s="9">
+        <v>0</v>
+      </c>
+      <c r="J121" s="12">
+        <v>0</v>
+      </c>
+      <c r="K121" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L121" s="9">
+        <v>0</v>
+      </c>
+      <c r="M121" s="10"/>
+      <c r="N121" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O121" s="10"/>
+      <c r="P121" s="11" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="122" spans="1:16">
+      <c r="A122" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="B122" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="C122" s="9">
+        <v>20</v>
+      </c>
+      <c r="D122" s="9">
+        <v>1</v>
+      </c>
+      <c r="E122" s="12">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="F122" s="9">
+        <v>20</v>
+      </c>
+      <c r="G122" s="9">
+        <v>20</v>
+      </c>
+      <c r="H122" s="9">
+        <v>0</v>
+      </c>
+      <c r="I122" s="9">
+        <v>0</v>
+      </c>
+      <c r="J122" s="12">
+        <v>0</v>
+      </c>
+      <c r="K122" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L122" s="9">
+        <v>0</v>
+      </c>
+      <c r="M122" s="10">
+        <v>12960</v>
+      </c>
+      <c r="N122" s="11">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="O122" s="10">
+        <v>3252</v>
+      </c>
+      <c r="P122" s="11">
+        <f t="shared" si="11"/>
+        <v>6.1500615006150061E-3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16">
+      <c r="A123" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B123" s="9"/>
+      <c r="C123" s="9">
+        <v>20</v>
+      </c>
+      <c r="D123" s="9">
+        <v>2</v>
+      </c>
+      <c r="E123" s="12">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F123" s="9">
+        <v>20</v>
+      </c>
+      <c r="G123" s="9">
+        <v>10</v>
+      </c>
+      <c r="H123" s="9">
+        <v>0</v>
+      </c>
+      <c r="I123" s="9">
+        <v>0</v>
+      </c>
+      <c r="J123" s="12">
+        <v>0</v>
+      </c>
+      <c r="K123" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L123" s="9">
+        <v>0</v>
+      </c>
+      <c r="M123" s="10"/>
+      <c r="N123" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O123" s="10"/>
+      <c r="P123" s="11" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="124" spans="1:16">
+      <c r="A124" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B124" s="9"/>
+      <c r="C124" s="9">
+        <v>20</v>
+      </c>
+      <c r="D124" s="9">
+        <v>1</v>
+      </c>
+      <c r="E124" s="12">
+        <v>1.44E-2</v>
+      </c>
+      <c r="F124" s="9">
+        <v>20</v>
+      </c>
+      <c r="G124" s="9">
+        <v>20</v>
+      </c>
+      <c r="H124" s="9">
+        <v>0</v>
+      </c>
+      <c r="I124" s="9">
+        <v>0</v>
+      </c>
+      <c r="J124" s="12">
+        <v>0</v>
+      </c>
+      <c r="K124" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L124" s="9">
+        <v>0</v>
+      </c>
+      <c r="M124" s="10"/>
+      <c r="N124" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O124" s="10"/>
+      <c r="P124" s="11" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="1:16">
+      <c r="A125" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B125" s="9"/>
+      <c r="C125" s="9">
+        <v>20</v>
+      </c>
+      <c r="D125" s="9">
+        <v>2</v>
+      </c>
+      <c r="E125" s="12">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F125" s="9">
+        <v>20</v>
+      </c>
+      <c r="G125" s="9">
+        <v>10</v>
+      </c>
+      <c r="H125" s="9">
+        <v>0</v>
+      </c>
+      <c r="I125" s="9">
+        <v>0</v>
+      </c>
+      <c r="J125" s="12">
+        <v>0</v>
+      </c>
+      <c r="K125" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L125" s="9">
+        <v>0</v>
+      </c>
+      <c r="M125" s="10"/>
+      <c r="N125" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O125" s="10"/>
+      <c r="P125" s="11" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:16">
+      <c r="A126" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="B126" s="9"/>
+      <c r="C126" s="9">
+        <v>20</v>
+      </c>
+      <c r="D126" s="9">
+        <v>2</v>
+      </c>
+      <c r="E126" s="12">
+        <v>1.4E-3</v>
+      </c>
+      <c r="F126" s="9">
+        <v>20</v>
+      </c>
+      <c r="G126" s="9">
+        <v>10</v>
+      </c>
+      <c r="H126" s="9">
+        <v>0</v>
+      </c>
+      <c r="I126" s="9">
+        <v>0</v>
+      </c>
+      <c r="J126" s="12">
+        <v>0</v>
+      </c>
+      <c r="K126" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L126" s="9">
+        <v>0</v>
+      </c>
+      <c r="M126" s="10"/>
+      <c r="N126" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O126" s="10"/>
+      <c r="P126" s="11" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="127" spans="1:16">
+      <c r="A127" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B127" s="9"/>
+      <c r="C127" s="9">
+        <v>20</v>
+      </c>
+      <c r="D127" s="9">
+        <v>1</v>
+      </c>
+      <c r="E127" s="12">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="F127" s="9">
+        <v>20</v>
+      </c>
+      <c r="G127" s="9">
+        <v>20</v>
+      </c>
+      <c r="H127" s="9">
+        <v>0</v>
+      </c>
+      <c r="I127" s="9">
+        <v>0</v>
+      </c>
+      <c r="J127" s="12">
+        <v>0</v>
+      </c>
+      <c r="K127" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L127" s="9">
+        <v>0</v>
+      </c>
+      <c r="M127" s="10"/>
+      <c r="N127" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O127" s="10"/>
+      <c r="P127" s="11" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="128" spans="1:16">
+      <c r="A128" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="B128" s="9"/>
+      <c r="C128" s="9">
+        <v>20</v>
+      </c>
+      <c r="D128" s="9">
+        <v>1</v>
+      </c>
+      <c r="E128" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F128" s="9">
+        <v>20</v>
+      </c>
+      <c r="G128" s="9">
+        <v>20</v>
+      </c>
+      <c r="H128" s="9">
+        <v>0</v>
+      </c>
+      <c r="I128" s="9">
+        <v>0</v>
+      </c>
+      <c r="J128" s="12">
+        <v>0</v>
+      </c>
+      <c r="K128" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L128" s="9">
+        <v>0</v>
+      </c>
+      <c r="M128" s="10"/>
+      <c r="N128" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O128" s="10"/>
+      <c r="P128" s="11" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="129" spans="1:16">
+      <c r="A129" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B129" s="9"/>
+      <c r="C129" s="9">
+        <v>20</v>
+      </c>
+      <c r="D129" s="9">
+        <v>1</v>
+      </c>
+      <c r="E129" s="12">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="F129" s="9">
+        <v>20</v>
+      </c>
+      <c r="G129" s="9">
+        <v>20</v>
+      </c>
+      <c r="H129" s="9">
+        <v>0</v>
+      </c>
+      <c r="I129" s="9">
+        <v>0</v>
+      </c>
+      <c r="J129" s="12">
+        <v>0</v>
+      </c>
+      <c r="K129" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L129" s="9">
+        <v>0</v>
+      </c>
+      <c r="M129" s="10"/>
+      <c r="N129" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O129" s="10"/>
+      <c r="P129" s="11" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="130" spans="1:16">
+      <c r="A130" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B130" s="9"/>
+      <c r="C130" s="9">
+        <v>20</v>
+      </c>
+      <c r="D130" s="9">
+        <v>2</v>
+      </c>
+      <c r="E130" s="12">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="F130" s="9">
+        <v>20</v>
+      </c>
+      <c r="G130" s="9">
+        <v>10</v>
+      </c>
+      <c r="H130" s="9">
+        <v>0</v>
+      </c>
+      <c r="I130" s="9">
+        <v>0</v>
+      </c>
+      <c r="J130" s="12">
+        <v>0</v>
+      </c>
+      <c r="K130" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L130" s="9">
+        <v>0</v>
+      </c>
+      <c r="M130" s="10"/>
+      <c r="N130" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O130" s="10"/>
+      <c r="P130" s="11" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="131" spans="1:16">
+      <c r="A131" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B131" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C131" s="9">
+        <v>20</v>
+      </c>
+      <c r="D131" s="9">
+        <v>1</v>
+      </c>
+      <c r="E131" s="12">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="F131" s="9">
+        <v>13</v>
+      </c>
+      <c r="G131" s="9">
+        <v>13</v>
+      </c>
+      <c r="H131" s="9">
+        <v>0</v>
+      </c>
+      <c r="I131" s="9">
+        <v>0</v>
+      </c>
+      <c r="J131" s="12">
+        <v>0</v>
+      </c>
+      <c r="K131" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L131" s="9">
+        <v>0</v>
+      </c>
+      <c r="M131" s="10">
+        <v>3960</v>
+      </c>
+      <c r="N131" s="11">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="O131" s="10">
+        <v>3366</v>
+      </c>
+      <c r="P131" s="11">
+        <f t="shared" si="11"/>
+        <v>3.8621509209744503E-3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16">
+      <c r="A132" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B132" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="C132" s="9">
+        <v>20</v>
+      </c>
+      <c r="D132" s="9">
+        <v>1</v>
+      </c>
+      <c r="E132" s="12">
+        <v>1E-4</v>
+      </c>
+      <c r="F132" s="9">
+        <v>12</v>
+      </c>
+      <c r="G132" s="9">
+        <v>12</v>
+      </c>
+      <c r="H132" s="9">
+        <v>0</v>
+      </c>
+      <c r="I132" s="9">
+        <v>0</v>
+      </c>
+      <c r="J132" s="12">
+        <v>0</v>
+      </c>
+      <c r="K132" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L132" s="9">
+        <v>0</v>
+      </c>
+      <c r="M132" s="10">
+        <v>9160</v>
+      </c>
+      <c r="N132" s="11">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="O132" s="10">
+        <v>7786</v>
+      </c>
+      <c r="P132" s="11">
+        <f t="shared" si="11"/>
+        <v>1.5412278448497304E-3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16">
+      <c r="A133" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B133" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="C133" s="9">
+        <v>20</v>
+      </c>
+      <c r="D133" s="9">
+        <v>1</v>
+      </c>
+      <c r="E133" s="12">
+        <v>1E-4</v>
+      </c>
+      <c r="F133" s="9">
+        <v>10</v>
+      </c>
+      <c r="G133" s="9">
+        <v>10</v>
+      </c>
+      <c r="H133" s="9">
+        <v>0</v>
+      </c>
+      <c r="I133" s="9">
+        <v>0</v>
+      </c>
+      <c r="J133" s="12">
+        <v>0</v>
+      </c>
+      <c r="K133" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L133" s="9">
+        <v>0</v>
+      </c>
+      <c r="M133" s="10">
+        <v>3980</v>
+      </c>
+      <c r="N133" s="11">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="O133" s="10">
+        <v>1060</v>
+      </c>
+      <c r="P133" s="11">
+        <f t="shared" si="11"/>
+        <v>9.433962264150943E-3</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16">
+      <c r="A134" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="B134" s="9"/>
+      <c r="C134" s="9">
+        <v>20</v>
+      </c>
+      <c r="D134" s="9">
+        <v>1</v>
+      </c>
+      <c r="E134" s="12">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="F134" s="9">
+        <v>10</v>
+      </c>
+      <c r="G134" s="9">
+        <v>10</v>
+      </c>
+      <c r="H134" s="9">
+        <v>0</v>
+      </c>
+      <c r="I134" s="9">
+        <v>0</v>
+      </c>
+      <c r="J134" s="12">
+        <v>0</v>
+      </c>
+      <c r="K134" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L134" s="9">
+        <v>0</v>
+      </c>
+      <c r="M134" s="10"/>
+      <c r="N134" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O134" s="10"/>
+      <c r="P134" s="11" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="135" spans="1:16">
+      <c r="A135" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D135" s="8">
+        <f>SUM(D13:D134)</f>
+        <v>3781</v>
+      </c>
+      <c r="F135" s="8">
+        <f>SUM(F13:F134)</f>
+        <v>53095</v>
+      </c>
+      <c r="H135" s="8">
+        <f>SUM(H13:H134)</f>
+        <v>218218</v>
+      </c>
+      <c r="I135" s="8">
+        <f>SUM(I13:I134)</f>
+        <v>64</v>
+      </c>
+      <c r="K135" s="14">
+        <f t="shared" si="9"/>
+        <v>4.10995385629532</v>
+      </c>
+      <c r="L135" s="8">
+        <f>SUM(L13:L134)</f>
+        <v>173900</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>